--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ235"/>
+  <dimension ref="A1:AJ236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>50000</v>
       </c>
       <c r="O6" t="n">
-        <v>125857.95</v>
+        <v>134445.61</v>
       </c>
       <c r="P6" t="n">
         <v>78988.2</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1789,16 +1789,16 @@
         <v>3127008</v>
       </c>
       <c r="R10" t="n">
-        <v>21740738.54</v>
+        <v>21860351.03</v>
       </c>
       <c r="S10" t="n">
-        <v>10881157.78</v>
+        <v>11231157.78</v>
       </c>
       <c r="T10" t="n">
-        <v>12475228.45</v>
+        <v>12825228.45</v>
       </c>
       <c r="U10" t="n">
-        <v>12428985.99</v>
+        <v>12548598.48</v>
       </c>
       <c r="V10" t="n">
         <v>1594070.67</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>207299.27</v>
+        <v>208352.16</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>10570590.51</v>
+        <v>11823903.46</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4583,19 +4583,19 @@
         <v>1306728.76</v>
       </c>
       <c r="P30" t="n">
-        <v>691663.77</v>
+        <v>692092.37</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2792576.67</v>
+        <v>2793005.27</v>
       </c>
       <c r="S30" t="n">
-        <v>1922786.24</v>
+        <v>1923214.84</v>
       </c>
       <c r="T30" t="n">
-        <v>2081783.02</v>
+        <v>2082211.62</v>
       </c>
       <c r="U30" t="n">
         <v>2100912.9</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3141258.4</v>
+        <v>3151167.44</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -4872,10 +4872,10 @@
         <v>24832306.47</v>
       </c>
       <c r="S32" t="n">
-        <v>18489073.68</v>
+        <v>18489264.06</v>
       </c>
       <c r="T32" t="n">
-        <v>22274038.09</v>
+        <v>22274228.47</v>
       </c>
       <c r="U32" t="n">
         <v>18677102.37</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>521128.68</v>
+        <v>523154.14</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
         <v>219000</v>
       </c>
       <c r="O47" t="n">
-        <v>182181.11</v>
+        <v>182623.58</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         <v>50000</v>
       </c>
       <c r="O55" t="n">
-        <v>24774.12</v>
+        <v>24792.87</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>317782.4</v>
+        <v>327691.44</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>7638.32</v>
+        <v>7661.58</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20129,7 +20129,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>170000</v>
+        <v>270000</v>
       </c>
       <c r="S141" t="n">
         <v>170000</v>
@@ -20138,7 +20138,7 @@
         <v>170000</v>
       </c>
       <c r="U141" t="n">
-        <v>170000</v>
+        <v>270000</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>30578.1</v>
+        <v>30603.28</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25707,20 +25707,20 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>138463.91</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>138463.91</v>
+        <v>0</v>
       </c>
       <c r="P181" t="n">
         <v>0</v>
@@ -25729,22 +25729,22 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>138463.91</v>
+        <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>138463.91</v>
+        <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
       </c>
       <c r="W181" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="X181" t="n">
         <v>0</v>
@@ -25756,7 +25756,7 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
         <v>5</v>
@@ -25784,17 +25784,17 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Luna</t>
+          <t>Emendas Parlamentares - Jair Tatto</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7027</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7017</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25847,20 +25847,20 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>100000</v>
+        <v>138463.91</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="O182" t="n">
-        <v>100000</v>
+        <v>138463.91</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -25869,22 +25869,22 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="S182" t="n">
-        <v>100000</v>
+        <v>138463.91</v>
       </c>
       <c r="T182" t="n">
-        <v>100000</v>
+        <v>138463.91</v>
       </c>
       <c r="U182" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
       </c>
       <c r="W182" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="X182" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="AB182" t="n">
         <v>5</v>
@@ -25924,17 +25924,17 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Rute Costa</t>
+          <t>Emendas Parlamentares - Luna</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7030</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7027</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -25987,20 +25987,20 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -26009,22 +26009,22 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="T183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
       </c>
       <c r="W183" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X183" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AB183" t="n">
         <v>5</v>
@@ -26064,17 +26064,17 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Sandra Santana</t>
+          <t>Emendas Parlamentares - Rute Costa</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7039</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7030</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26127,7 +26127,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -26137,7 +26137,7 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>230000</v>
+        <v>50000</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -26149,22 +26149,22 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
       </c>
       <c r="W184" t="n">
-        <v>230000</v>
+        <v>50000</v>
       </c>
       <c r="X184" t="n">
         <v>0</v>
@@ -26176,7 +26176,7 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>230000</v>
+        <v>50000</v>
       </c>
       <c r="AB184" t="n">
         <v>5</v>
@@ -26204,17 +26204,17 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Sansão Pereira</t>
+          <t>Emendas Parlamentares - Sandra Santana</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7041</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7039</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26267,7 +26267,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -26277,7 +26277,7 @@
         <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -26289,22 +26289,22 @@
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="S185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="U185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="X185" t="n">
         <v>0</v>
@@ -26316,7 +26316,7 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="AB185" t="n">
         <v>5</v>
@@ -26344,17 +26344,17 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Silvia Ferraro</t>
+          <t>Emendas Parlamentares - Sansão Pereira</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7047</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7041</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26407,20 +26407,20 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
         <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -26429,22 +26429,22 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="T186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="U186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
       </c>
       <c r="W186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="X186" t="n">
         <v>0</v>
@@ -26456,7 +26456,7 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
         <v>5</v>
@@ -26484,17 +26484,17 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Senival Moura</t>
+          <t>Emendas Parlamentares - Silvia Ferraro</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7047</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26547,20 +26547,20 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="O187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
@@ -26569,22 +26569,22 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="S187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="T187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="U187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
       </c>
       <c r="W187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="X187" t="n">
         <v>0</v>
@@ -26596,7 +26596,7 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="AB187" t="n">
         <v>5</v>
@@ -26624,17 +26624,17 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Toninho Vespoli</t>
+          <t>Emendas Parlamentares - Senival Moura</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7049</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26687,7 +26687,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -26697,7 +26697,7 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>475000</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -26724,7 +26724,7 @@
         <v>0</v>
       </c>
       <c r="W188" t="n">
-        <v>475000</v>
+        <v>0</v>
       </c>
       <c r="X188" t="n">
         <v>0</v>
@@ -26736,7 +26736,7 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>475000</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
         <v>5</v>
@@ -26764,17 +26764,17 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Hélio Rodrigues</t>
+          <t>Emendas Parlamentares - Toninho Vespoli</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7050</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7049</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26827,20 +26827,20 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>261000</v>
+        <v>475000</v>
       </c>
       <c r="O189" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -26849,22 +26849,22 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
       </c>
       <c r="W189" t="n">
-        <v>261000</v>
+        <v>475000</v>
       </c>
       <c r="X189" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>261000</v>
+        <v>475000</v>
       </c>
       <c r="AB189" t="n">
         <v>5</v>
@@ -26904,17 +26904,17 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Ana Carolina Oliveira</t>
+          <t>Emendas Parlamentares - Hélio Rodrigues</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7070</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7050</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -26967,20 +26967,20 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>110244.42</v>
+        <v>261000</v>
       </c>
       <c r="O190" t="n">
-        <v>57000</v>
+        <v>150000</v>
       </c>
       <c r="P190" t="n">
         <v>0</v>
@@ -26989,22 +26989,22 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="S190" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="T190" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="U190" t="n">
-        <v>57000</v>
+        <v>261000</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
       </c>
       <c r="W190" t="n">
-        <v>110244.42</v>
+        <v>261000</v>
       </c>
       <c r="X190" t="n">
         <v>0</v>
@@ -27016,7 +27016,7 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>110244.42</v>
+        <v>261000</v>
       </c>
       <c r="AB190" t="n">
         <v>5</v>
@@ -27044,17 +27044,17 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Emendas Parlamentares - Ana Carolina Oliveira</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7070</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27107,20 +27107,20 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="M191" t="n">
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>712872.0600000001</v>
+        <v>110244.42</v>
       </c>
       <c r="O191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
@@ -27129,22 +27129,22 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="S191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="T191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="U191" t="n">
-        <v>452872.05</v>
+        <v>57000</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>
       </c>
       <c r="W191" t="n">
-        <v>712872.0600000001</v>
+        <v>110244.42</v>
       </c>
       <c r="X191" t="n">
         <v>0</v>
@@ -27156,7 +27156,7 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>712872.0600000001</v>
+        <v>110244.42</v>
       </c>
       <c r="AB191" t="n">
         <v>5</v>
@@ -27184,17 +27184,17 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Lucas Pavanato</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27247,20 +27247,20 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="O192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="P192" t="n">
         <v>0</v>
@@ -27269,22 +27269,22 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="S192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="T192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="U192" t="n">
-        <v>318150</v>
+        <v>452872.05</v>
       </c>
       <c r="V192" t="n">
         <v>0</v>
       </c>
       <c r="W192" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="X192" t="n">
         <v>0</v>
@@ -27296,7 +27296,7 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>318150</v>
+        <v>712872.0600000001</v>
       </c>
       <c r="AB192" t="n">
         <v>5</v>
@@ -27324,17 +27324,17 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Zoe Martínez</t>
+          <t>Emendas Parlamentares - Lucas Pavanato</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7087</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -27387,56 +27387,56 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>7107600</v>
+        <v>318150</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>960000</v>
+        <v>318150</v>
       </c>
       <c r="O193" t="n">
-        <v>7107600</v>
+        <v>318150</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="S193" t="n">
-        <v>7935600</v>
+        <v>318150</v>
       </c>
       <c r="T193" t="n">
-        <v>8889200</v>
+        <v>318150</v>
       </c>
       <c r="U193" t="n">
-        <v>9076439.67</v>
+        <v>318150</v>
       </c>
       <c r="V193" t="n">
-        <v>953600</v>
+        <v>0</v>
       </c>
       <c r="W193" t="n">
-        <v>9665439.67</v>
+        <v>318150</v>
       </c>
       <c r="X193" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>9665439.67</v>
+        <v>318150</v>
       </c>
       <c r="AB193" t="n">
         <v>5</v>
@@ -27459,22 +27459,22 @@
       </c>
       <c r="AG193" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Zoe Martínez</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7087</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27507,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -27531,52 +27531,52 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>24545612.47</v>
+        <v>7935600</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>8495211.470000001</v>
+        <v>960000</v>
       </c>
       <c r="O194" t="n">
-        <v>24545612.47</v>
+        <v>7107600</v>
       </c>
       <c r="P194" t="n">
-        <v>1885306.26</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="R194" t="n">
-        <v>32806875.73</v>
+        <v>9076439.67</v>
       </c>
       <c r="S194" t="n">
-        <v>25225912.81</v>
+        <v>7935600</v>
       </c>
       <c r="T194" t="n">
-        <v>25892927.01</v>
+        <v>8889200</v>
       </c>
       <c r="U194" t="n">
-        <v>30921569.47</v>
+        <v>9076439.67</v>
       </c>
       <c r="V194" t="n">
-        <v>667014.2</v>
+        <v>953600</v>
       </c>
       <c r="W194" t="n">
-        <v>30921569.47</v>
+        <v>9665439.67</v>
       </c>
       <c r="X194" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="Y194" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA194" t="n">
-        <v>30921569.47</v>
+        <v>9665439.67</v>
       </c>
       <c r="AB194" t="n">
         <v>5</v>
@@ -27589,7 +27589,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="AG194" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH194" t="inlineStr">
@@ -27609,12 +27609,12 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27657,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -27671,52 +27671,52 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>90884.2</v>
+        <v>24545612.47</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>52998</v>
+        <v>8495211.470000001</v>
       </c>
       <c r="O195" t="n">
-        <v>89160.2</v>
+        <v>24545612.47</v>
       </c>
       <c r="P195" t="n">
-        <v>66171.82000000001</v>
+        <v>5412701.99</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>267909.15</v>
+        <v>36334268.46</v>
       </c>
       <c r="S195" t="n">
-        <v>161394.12</v>
+        <v>29716613.12</v>
       </c>
       <c r="T195" t="n">
-        <v>164926.33</v>
+        <v>30650929.58</v>
       </c>
       <c r="U195" t="n">
-        <v>201737.33</v>
+        <v>30921566.47</v>
       </c>
       <c r="V195" t="n">
-        <v>3532.21</v>
+        <v>934316.46</v>
       </c>
       <c r="W195" t="n">
-        <v>232998</v>
+        <v>30921569.47</v>
       </c>
       <c r="X195" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="Y195" t="n">
         <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>232998</v>
+        <v>30921569.47</v>
       </c>
       <c r="AB195" t="n">
         <v>5</v>
@@ -27739,7 +27739,7 @@
       </c>
       <c r="AG195" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH195" t="inlineStr">
@@ -27749,12 +27749,12 @@
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -27811,52 +27811,52 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>97412.85000000001</v>
+        <v>90884.2</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>52998</v>
       </c>
       <c r="O196" t="n">
-        <v>95912.85000000001</v>
+        <v>89160.2</v>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>66171.82000000001</v>
       </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>144434.93</v>
+        <v>267909.15</v>
       </c>
       <c r="S196" t="n">
-        <v>144434.93</v>
+        <v>161394.12</v>
       </c>
       <c r="T196" t="n">
-        <v>144434.93</v>
+        <v>164926.33</v>
       </c>
       <c r="U196" t="n">
-        <v>144434.93</v>
+        <v>201737.33</v>
       </c>
       <c r="V196" t="n">
-        <v>0</v>
+        <v>3532.21</v>
       </c>
       <c r="W196" t="n">
-        <v>144434.93</v>
+        <v>232998</v>
       </c>
       <c r="X196" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Y196" t="n">
         <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>105565.07</v>
+        <v>20000</v>
       </c>
       <c r="AA196" t="n">
-        <v>144434.93</v>
+        <v>232998</v>
       </c>
       <c r="AB196" t="n">
         <v>5</v>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="AG196" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH196" t="inlineStr">
@@ -27889,12 +27889,12 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -27951,7 +27951,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>898725.67</v>
+        <v>97412.85000000001</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -27960,43 +27960,43 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>869016.0600000001</v>
+        <v>95912.85000000001</v>
       </c>
       <c r="P197" t="n">
-        <v>1760683.97</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>4263497.9</v>
+        <v>144434.93</v>
       </c>
       <c r="S197" t="n">
-        <v>1620855.47</v>
+        <v>144434.93</v>
       </c>
       <c r="T197" t="n">
-        <v>1687781.31</v>
+        <v>144434.93</v>
       </c>
       <c r="U197" t="n">
-        <v>2502813.93</v>
+        <v>144434.93</v>
       </c>
       <c r="V197" t="n">
-        <v>66925.84</v>
+        <v>0</v>
       </c>
       <c r="W197" t="n">
-        <v>2512525.33</v>
+        <v>144434.93</v>
       </c>
       <c r="X197" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="Y197" t="n">
         <v>0</v>
       </c>
       <c r="Z197" t="n">
-        <v>25401.67</v>
+        <v>105565.07</v>
       </c>
       <c r="AA197" t="n">
-        <v>2512525.33</v>
+        <v>144434.93</v>
       </c>
       <c r="AB197" t="n">
         <v>5</v>
@@ -28019,7 +28019,7 @@
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH197" t="inlineStr">
@@ -28029,12 +28029,12 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -28091,7 +28091,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1736975.36</v>
+        <v>908634.71</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
@@ -28100,43 +28100,43 @@
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>1625643.01</v>
+        <v>869016.0600000001</v>
       </c>
       <c r="P198" t="n">
-        <v>2763223.97</v>
+        <v>1760683.97</v>
       </c>
       <c r="Q198" t="n">
-        <v>65487</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>6089210.8</v>
+        <v>4263497.9</v>
       </c>
       <c r="S198" t="n">
-        <v>2482175.87</v>
+        <v>1620855.47</v>
       </c>
       <c r="T198" t="n">
-        <v>2586523.63</v>
+        <v>1687781.31</v>
       </c>
       <c r="U198" t="n">
-        <v>3325986.83</v>
+        <v>2502813.93</v>
       </c>
       <c r="V198" t="n">
-        <v>104347.76</v>
+        <v>66925.84</v>
       </c>
       <c r="W198" t="n">
-        <v>3328090.03</v>
+        <v>2512525.33</v>
       </c>
       <c r="X198" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="Y198" t="n">
-        <v>65487</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>1477958.97</v>
+        <v>25401.67</v>
       </c>
       <c r="AA198" t="n">
-        <v>3328090.03</v>
+        <v>2512525.33</v>
       </c>
       <c r="AB198" t="n">
         <v>5</v>
@@ -28159,7 +28159,7 @@
       </c>
       <c r="AG198" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH198" t="inlineStr">
@@ -28169,12 +28169,12 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28227,11 +28227,11 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>368.19</v>
+        <v>1736975.36</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28240,43 +28240,43 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>368.19</v>
+        <v>1625643.01</v>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>2763223.97</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>65487</v>
       </c>
       <c r="R199" t="n">
-        <v>80100</v>
+        <v>6089210.8</v>
       </c>
       <c r="S199" t="n">
-        <v>73100</v>
+        <v>2482175.87</v>
       </c>
       <c r="T199" t="n">
-        <v>80100</v>
+        <v>2586523.63</v>
       </c>
       <c r="U199" t="n">
-        <v>80100</v>
+        <v>3325986.83</v>
       </c>
       <c r="V199" t="n">
-        <v>7000</v>
+        <v>104347.76</v>
       </c>
       <c r="W199" t="n">
-        <v>139282</v>
+        <v>3328090.03</v>
       </c>
       <c r="X199" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>65487</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>1477958.97</v>
       </c>
       <c r="AA199" t="n">
-        <v>139282</v>
+        <v>3328090.03</v>
       </c>
       <c r="AB199" t="n">
         <v>5</v>
@@ -28304,17 +28304,17 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -28367,11 +28367,11 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>15742.8</v>
+        <v>368.19</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
@@ -28380,7 +28380,7 @@
         <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>15742.8</v>
+        <v>368.19</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -28389,25 +28389,25 @@
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="S200" t="n">
-        <v>19678.5</v>
+        <v>73100</v>
       </c>
       <c r="T200" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="U200" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="V200" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="W200" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X200" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="Y200" t="n">
         <v>0</v>
@@ -28416,7 +28416,7 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AB200" t="n">
         <v>5</v>
@@ -28439,22 +28439,22 @@
       </c>
       <c r="AG200" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28487,17 +28487,17 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>15742.8</v>
       </c>
       <c r="M201" t="n">
         <v>0</v>
@@ -28520,43 +28520,43 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
+        <v>15742.8</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S201" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V201" t="n">
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X201" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="Y201" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="Z201" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="AB201" t="n">
         <v>5</v>
@@ -28564,12 +28564,12 @@
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="AG201" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH201" t="inlineStr">
@@ -28589,12 +28589,12 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -28687,13 +28687,13 @@
         <v>0</v>
       </c>
       <c r="X202" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y202" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="Z202" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA202" t="n">
         <v>0</v>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -28729,12 +28729,12 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -28806,7 +28806,7 @@
         <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
@@ -28827,13 +28827,13 @@
         <v>0</v>
       </c>
       <c r="X203" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y203" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="Z203" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA203" t="n">
         <v>0</v>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -28869,12 +28869,12 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -28903,16 +28903,16 @@
         <v>422</v>
       </c>
       <c r="F204" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -28927,7 +28927,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L204" t="n">
@@ -28937,7 +28937,7 @@
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -28946,10 +28946,10 @@
         <v>0</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R204" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -28958,25 +28958,25 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V204" t="n">
         <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X204" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y204" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA204" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
         <v>5</v>
@@ -28984,12 +28984,12 @@
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -29004,17 +29004,17 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Luana Alves</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33503900.00.1.500.7026</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -29067,7 +29067,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="L205" t="n">
@@ -29077,7 +29077,7 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -29089,7 +29089,7 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -29098,16 +29098,16 @@
         <v>0</v>
       </c>
       <c r="U205" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V205" t="n">
         <v>0</v>
       </c>
       <c r="W205" t="n">
-        <v>11949</v>
+        <v>200000</v>
       </c>
       <c r="X205" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="Y205" t="n">
         <v>0</v>
@@ -29116,7 +29116,7 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>11949</v>
+        <v>200000</v>
       </c>
       <c r="AB205" t="n">
         <v>5</v>
@@ -29139,22 +29139,22 @@
       </c>
       <c r="AG205" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Luana Alves</t>
         </is>
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33503900.00.1.500.7026</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29187,7 +29187,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -29211,52 +29211,52 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2704790.67</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="P206" t="n">
-        <v>1098604.07</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>10258886.74</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>7909901.72</v>
+        <v>0</v>
       </c>
       <c r="T206" t="n">
-        <v>9008505.779999999</v>
+        <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>9160282.67</v>
+        <v>0</v>
       </c>
       <c r="V206" t="n">
-        <v>1098604.06</v>
+        <v>0</v>
       </c>
       <c r="W206" t="n">
-        <v>9160282.67</v>
+        <v>11949</v>
       </c>
       <c r="X206" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="Y206" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Z206" t="n">
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>9160282.67</v>
+        <v>11949</v>
       </c>
       <c r="AB206" t="n">
         <v>5</v>
@@ -29269,7 +29269,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -29279,7 +29279,7 @@
       </c>
       <c r="AG206" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH206" t="inlineStr">
@@ -29289,12 +29289,12 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -29351,52 +29351,52 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>9864</v>
+        <v>7909901.72</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>2704790.67</v>
       </c>
       <c r="O207" t="n">
-        <v>9864</v>
+        <v>7909901.72</v>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1098604.07</v>
       </c>
       <c r="Q207" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="R207" t="n">
-        <v>9991.799999999999</v>
+        <v>10258886.74</v>
       </c>
       <c r="S207" t="n">
-        <v>9864</v>
+        <v>7909901.72</v>
       </c>
       <c r="T207" t="n">
-        <v>9864</v>
+        <v>9008505.779999999</v>
       </c>
       <c r="U207" t="n">
-        <v>9991.799999999999</v>
+        <v>9160282.67</v>
       </c>
       <c r="V207" t="n">
-        <v>0</v>
+        <v>1098604.06</v>
       </c>
       <c r="W207" t="n">
-        <v>10000</v>
+        <v>9160282.67</v>
       </c>
       <c r="X207" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="Y207" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Z207" t="n">
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>10000</v>
+        <v>9160282.67</v>
       </c>
       <c r="AB207" t="n">
         <v>5</v>
@@ -29419,7 +29419,7 @@
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
@@ -29429,12 +29429,12 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -29500,43 +29500,43 @@
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="R208" t="n">
-        <v>80612</v>
+        <v>9991.799999999999</v>
       </c>
       <c r="S208" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>9864</v>
       </c>
       <c r="U208" t="n">
-        <v>80612</v>
+        <v>9991.799999999999</v>
       </c>
       <c r="V208" t="n">
         <v>0</v>
       </c>
       <c r="W208" t="n">
-        <v>80612</v>
+        <v>10000</v>
       </c>
       <c r="X208" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="Y208" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Z208" t="n">
-        <v>69388</v>
+        <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>80612</v>
+        <v>10000</v>
       </c>
       <c r="AB208" t="n">
         <v>5</v>
@@ -29559,7 +29559,7 @@
       </c>
       <c r="AG208" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH208" t="inlineStr">
@@ -29569,12 +29569,12 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29617,7 +29617,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -29631,7 +29631,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>356543.33</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
@@ -29640,43 +29640,43 @@
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>318270.87</v>
+        <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>4837262.97</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>5886824</v>
+        <v>69388</v>
       </c>
       <c r="R209" t="n">
-        <v>7758858.94</v>
+        <v>80612</v>
       </c>
       <c r="S209" t="n">
-        <v>559609.14</v>
+        <v>0</v>
       </c>
       <c r="T209" t="n">
-        <v>2453838.77</v>
+        <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>2921595.97</v>
+        <v>80612</v>
       </c>
       <c r="V209" t="n">
-        <v>1894229.63</v>
+        <v>0</v>
       </c>
       <c r="W209" t="n">
-        <v>2921595.97</v>
+        <v>80612</v>
       </c>
       <c r="X209" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="Y209" t="n">
-        <v>5886824</v>
+        <v>69388</v>
       </c>
       <c r="Z209" t="n">
-        <v>8003766.03</v>
+        <v>69388</v>
       </c>
       <c r="AA209" t="n">
-        <v>2921595.97</v>
+        <v>80612</v>
       </c>
       <c r="AB209" t="n">
         <v>5</v>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="AG209" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH209" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29767,11 +29767,11 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>296.92</v>
+        <v>356543.33</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29780,43 +29780,43 @@
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>296.92</v>
+        <v>318270.87</v>
       </c>
       <c r="P210" t="n">
-        <v>925</v>
+        <v>4837262.97</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>5886824</v>
       </c>
       <c r="R210" t="n">
-        <v>1900</v>
+        <v>7758858.94</v>
       </c>
       <c r="S210" t="n">
-        <v>975</v>
+        <v>559609.14</v>
       </c>
       <c r="T210" t="n">
-        <v>975</v>
+        <v>2453838.77</v>
       </c>
       <c r="U210" t="n">
-        <v>975</v>
+        <v>2921595.97</v>
       </c>
       <c r="V210" t="n">
-        <v>0</v>
+        <v>1894229.63</v>
       </c>
       <c r="W210" t="n">
-        <v>1000</v>
+        <v>2921595.97</v>
       </c>
       <c r="X210" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>5886824</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>8003766.03</v>
       </c>
       <c r="AA210" t="n">
-        <v>1000</v>
+        <v>2921595.97</v>
       </c>
       <c r="AB210" t="n">
         <v>5</v>
@@ -29844,17 +29844,17 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -29887,17 +29887,17 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -29907,11 +29907,11 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>296.92</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29920,43 +29920,43 @@
         <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>296.92</v>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="Q211" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="S211" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="T211" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="U211" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="V211" t="n">
         <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X211" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="Y211" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB211" t="n">
         <v>5</v>
@@ -29964,12 +29964,12 @@
       <c r="AC211" t="inlineStr"/>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -29979,22 +29979,22 @@
       </c>
       <c r="AG211" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30020,24 +30020,24 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F212" t="n">
         <v>4026</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -30051,7 +30051,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>31100</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -30060,43 +30060,43 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="P212" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="R212" t="n">
-        <v>50100</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>38100</v>
+        <v>0</v>
       </c>
       <c r="T212" t="n">
-        <v>38700</v>
+        <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>38700</v>
+        <v>0</v>
       </c>
       <c r="V212" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="W212" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="X212" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="Y212" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA212" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
         <v>5</v>
@@ -30104,12 +30104,12 @@
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -30119,7 +30119,7 @@
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
@@ -30129,12 +30129,12 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -30191,52 +30191,52 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>77753</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="P213" t="n">
-        <v>19140.97</v>
+        <v>11400</v>
       </c>
       <c r="Q213" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="R213" t="n">
-        <v>95090.62</v>
+        <v>50100</v>
       </c>
       <c r="S213" t="n">
-        <v>42280.65</v>
+        <v>38100</v>
       </c>
       <c r="T213" t="n">
-        <v>42280.65</v>
+        <v>38700</v>
       </c>
       <c r="U213" t="n">
-        <v>75949.64999999999</v>
+        <v>38700</v>
       </c>
       <c r="V213" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="W213" t="n">
-        <v>111422</v>
+        <v>46881</v>
       </c>
       <c r="X213" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="Y213" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Z213" t="n">
-        <v>187297</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>111422</v>
+        <v>46881</v>
       </c>
       <c r="AB213" t="n">
         <v>5</v>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="AG213" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH213" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30307,17 +30307,17 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -30337,46 +30337,46 @@
         <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>77753</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q214" t="n">
-        <v>155746.65</v>
+        <v>187297</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>95090.62</v>
       </c>
       <c r="S214" t="n">
-        <v>0</v>
+        <v>42280.65</v>
       </c>
       <c r="T214" t="n">
-        <v>0</v>
+        <v>42280.65</v>
       </c>
       <c r="U214" t="n">
-        <v>0</v>
+        <v>75949.64999999999</v>
       </c>
       <c r="V214" t="n">
         <v>0</v>
       </c>
       <c r="W214" t="n">
-        <v>0</v>
+        <v>111422</v>
       </c>
       <c r="X214" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="Y214" t="n">
-        <v>155747.3</v>
+        <v>187297</v>
       </c>
       <c r="Z214" t="n">
-        <v>99999.35000000001</v>
+        <v>187297</v>
       </c>
       <c r="AA214" t="n">
-        <v>0.65</v>
+        <v>111422</v>
       </c>
       <c r="AB214" t="n">
         <v>5</v>
@@ -30384,12 +30384,12 @@
       <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="AG214" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH214" t="inlineStr">
@@ -30409,12 +30409,12 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30426,12 +30426,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30440,19 +30440,19 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F215" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -30467,7 +30467,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L215" t="n">
@@ -30477,7 +30477,7 @@
         <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>155746.65</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -30504,19 +30504,19 @@
         <v>0</v>
       </c>
       <c r="W215" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="X215" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>155747.3</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>99999.35000000001</v>
       </c>
       <c r="AA215" t="n">
-        <v>400000</v>
+        <v>0.65</v>
       </c>
       <c r="AB215" t="n">
         <v>5</v>
@@ -30524,12 +30524,12 @@
       <c r="AC215" t="inlineStr"/>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -30544,17 +30544,17 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Luna</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7027</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30607,7 +30607,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -30617,7 +30617,7 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>170000</v>
+        <v>400000</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -30644,7 +30644,7 @@
         <v>0</v>
       </c>
       <c r="W216" t="n">
-        <v>170000</v>
+        <v>400000</v>
       </c>
       <c r="X216" t="n">
         <v>0</v>
@@ -30656,7 +30656,7 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>170000</v>
+        <v>400000</v>
       </c>
       <c r="AB216" t="n">
         <v>5</v>
@@ -30684,17 +30684,17 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Silvia Ferraro</t>
+          <t>Emendas Parlamentares - Luna</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7047</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7027</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30747,20 +30747,20 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="L217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="O217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -30769,22 +30769,22 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V217" t="n">
         <v>0</v>
       </c>
       <c r="W217" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="X217" t="n">
         <v>0</v>
@@ -30796,7 +30796,7 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="AB217" t="n">
         <v>5</v>
@@ -30824,17 +30824,17 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Emendas Parlamentares - Silvia Ferraro</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7047</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -30887,20 +30887,20 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="O218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -30909,22 +30909,22 @@
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="S218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="T218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="U218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="V218" t="n">
         <v>0</v>
       </c>
       <c r="W218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="X218" t="n">
         <v>0</v>
@@ -30936,7 +30936,7 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="AB218" t="n">
         <v>5</v>
@@ -30964,17 +30964,17 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Marina Bragante</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7079</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31017,7 +31017,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -31027,56 +31027,56 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
       </c>
       <c r="Q219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V219" t="n">
         <v>0</v>
       </c>
       <c r="W219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AB219" t="n">
         <v>5</v>
@@ -31099,65 +31099,65 @@
       </c>
       <c r="AG219" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Marina Bragante</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7079</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F220" t="n">
         <v>4010</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -31171,52 +31171,52 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>34668633.7</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
         <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>5686650.13</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>34668633.7</v>
+        <v>0</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="R220" t="n">
-        <v>46522205.13</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>46522205.12</v>
+        <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>46522205.12</v>
+        <v>0</v>
       </c>
       <c r="U220" t="n">
-        <v>46522205.13</v>
+        <v>0</v>
       </c>
       <c r="V220" t="n">
         <v>0</v>
       </c>
       <c r="W220" t="n">
-        <v>46522205.13</v>
+        <v>0</v>
       </c>
       <c r="X220" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y220" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z220" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="AA220" t="n">
-        <v>46522205.13</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
         <v>5</v>
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="AG220" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH220" t="inlineStr">
@@ -31249,12 +31249,12 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -31311,52 +31311,52 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>38440789.58</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>5686650.13</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>34668633.7</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
       </c>
       <c r="Q221" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>46522205.13</v>
       </c>
       <c r="S221" t="n">
-        <v>0</v>
+        <v>46522205.12</v>
       </c>
       <c r="T221" t="n">
-        <v>0</v>
+        <v>46522205.12</v>
       </c>
       <c r="U221" t="n">
-        <v>0</v>
+        <v>46522205.13</v>
       </c>
       <c r="V221" t="n">
         <v>0</v>
       </c>
       <c r="W221" t="n">
-        <v>600437</v>
+        <v>46522205.13</v>
       </c>
       <c r="X221" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y221" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>600437</v>
+        <v>46522205.13</v>
       </c>
       <c r="AB221" t="n">
         <v>5</v>
@@ -31379,7 +31379,7 @@
       </c>
       <c r="AG221" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH221" t="inlineStr">
@@ -31389,12 +31389,12 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31416,23 +31416,23 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F222" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -31466,7 +31466,7 @@
         <v>0</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -31484,19 +31484,19 @@
         <v>0</v>
       </c>
       <c r="W222" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X222" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="AA222" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="AB222" t="n">
         <v>5</v>
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -31529,12 +31529,12 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -31597,7 +31597,7 @@
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -31609,7 +31609,7 @@
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -31618,16 +31618,16 @@
         <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V223" t="n">
         <v>0</v>
       </c>
       <c r="W223" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="X223" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y223" t="n">
         <v>0</v>
@@ -31636,7 +31636,7 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="AB223" t="n">
         <v>5</v>
@@ -31659,7 +31659,7 @@
       </c>
       <c r="AG223" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH223" t="inlineStr">
@@ -31669,12 +31669,12 @@
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31700,14 +31700,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F224" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -31717,7 +31717,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -31731,52 +31731,52 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>145410701.45</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O224" t="n">
-        <v>143327924.45</v>
+        <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>50520982.11</v>
+        <v>0</v>
       </c>
       <c r="Q224" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>216235104.06</v>
+        <v>361510</v>
       </c>
       <c r="S224" t="n">
-        <v>163869845.15</v>
+        <v>0</v>
       </c>
       <c r="T224" t="n">
-        <v>170144602.81</v>
+        <v>0</v>
       </c>
       <c r="U224" t="n">
-        <v>165714121.95</v>
+        <v>361510</v>
       </c>
       <c r="V224" t="n">
-        <v>6274757.66</v>
+        <v>0</v>
       </c>
       <c r="W224" t="n">
-        <v>165715582</v>
+        <v>361510</v>
       </c>
       <c r="X224" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>6097457</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>165715582</v>
+        <v>361510</v>
       </c>
       <c r="AB224" t="n">
         <v>5</v>
@@ -31789,7 +31789,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="AG224" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH224" t="inlineStr">
@@ -31809,12 +31809,12 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -31857,21 +31857,21 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>145445519.3</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31880,43 +31880,43 @@
         <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>143327924.45</v>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>50520982.11</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>216235104.06</v>
       </c>
       <c r="S225" t="n">
-        <v>0</v>
+        <v>164527540.7</v>
       </c>
       <c r="T225" t="n">
-        <v>0</v>
+        <v>170802298.36</v>
       </c>
       <c r="U225" t="n">
-        <v>0</v>
+        <v>165714121.95</v>
       </c>
       <c r="V225" t="n">
-        <v>0</v>
+        <v>6274757.66</v>
       </c>
       <c r="W225" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="X225" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>6097457</v>
       </c>
       <c r="AA225" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="AB225" t="n">
         <v>5</v>
@@ -31934,27 +31934,27 @@
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG225" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32002,12 +32002,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L226" t="n">
@@ -32044,10 +32044,10 @@
         <v>0</v>
       </c>
       <c r="W226" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X226" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y226" t="n">
         <v>0</v>
@@ -32056,7 +32056,7 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB226" t="n">
         <v>5</v>
@@ -32074,7 +32074,7 @@
       </c>
       <c r="AF226" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG226" t="inlineStr">
@@ -32084,17 +32084,17 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32137,21 +32137,21 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L227" t="n">
-        <v>83680665.70999999</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -32160,43 +32160,43 @@
         <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>79306283.70999999</v>
+        <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>80527720</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>217416742</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>121904379.2</v>
+        <v>0</v>
       </c>
       <c r="T227" t="n">
-        <v>121904379.2</v>
+        <v>0</v>
       </c>
       <c r="U227" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V227" t="n">
         <v>0</v>
       </c>
       <c r="W227" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X227" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y227" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="AB227" t="n">
         <v>5</v>
@@ -32214,27 +32214,27 @@
       </c>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG227" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -32291,7 +32291,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>62065695.96</v>
+        <v>83680665.70999999</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -32300,43 +32300,43 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>61218639.72</v>
+        <v>79306283.70999999</v>
       </c>
       <c r="P228" t="n">
-        <v>51388595.59</v>
+        <v>80527720</v>
       </c>
       <c r="Q228" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="R228" t="n">
-        <v>130831621.59</v>
+        <v>217416742</v>
       </c>
       <c r="S228" t="n">
-        <v>78778260.98999999</v>
+        <v>121904379.2</v>
       </c>
       <c r="T228" t="n">
-        <v>99672054.66</v>
+        <v>121904379.2</v>
       </c>
       <c r="U228" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V228" t="n">
-        <v>20893793.67</v>
+        <v>0</v>
       </c>
       <c r="W228" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X228" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y228" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z228" t="n">
-        <v>4199097</v>
+        <v>4727853</v>
       </c>
       <c r="AA228" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="AB228" t="n">
         <v>5</v>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="AG228" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH228" t="inlineStr">
@@ -32369,12 +32369,12 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32422,16 +32422,16 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>62279940.24</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,43 +32440,43 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>61551749.34</v>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>51388595.59</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>130831621.59</v>
       </c>
       <c r="S229" t="n">
-        <v>0</v>
+        <v>78778260.98999999</v>
       </c>
       <c r="T229" t="n">
-        <v>0</v>
+        <v>99672054.66</v>
       </c>
       <c r="U229" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V229" t="n">
-        <v>0</v>
+        <v>20893793.67</v>
       </c>
       <c r="W229" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X229" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>4199097</v>
       </c>
       <c r="AA229" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="AB229" t="n">
         <v>5</v>
@@ -32494,7 +32494,7 @@
       </c>
       <c r="AF229" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG229" t="inlineStr">
@@ -32504,17 +32504,17 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32557,30 +32557,30 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L230" t="n">
-        <v>907561.39</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>907561.39</v>
+        <v>0</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -32589,25 +32589,25 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>1373122.99</v>
+        <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U230" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V230" t="n">
-        <v>33597.01</v>
+        <v>0</v>
       </c>
       <c r="W230" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X230" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y230" t="n">
         <v>0</v>
@@ -32616,7 +32616,7 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB230" t="n">
         <v>5</v>
@@ -32634,39 +32634,39 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -32680,24 +32680,24 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F231" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -32711,16 +32711,16 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>907561.39</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>907561.39</v>
       </c>
       <c r="P231" t="n">
         <v>0</v>
@@ -32729,25 +32729,25 @@
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S231" t="n">
-        <v>0</v>
+        <v>1373122.99</v>
       </c>
       <c r="T231" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V231" t="n">
-        <v>0</v>
+        <v>33597.01</v>
       </c>
       <c r="W231" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X231" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y231" t="n">
         <v>0</v>
@@ -32756,7 +32756,7 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB231" t="n">
         <v>5</v>
@@ -32764,12 +32764,12 @@
       <c r="AC231" t="inlineStr"/>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="AG231" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH231" t="inlineStr">
@@ -32789,12 +32789,12 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32837,7 +32837,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -32884,10 +32884,10 @@
         <v>0</v>
       </c>
       <c r="W232" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X232" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y232" t="n">
         <v>0</v>
@@ -32896,7 +32896,7 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB232" t="n">
         <v>5</v>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="AG232" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH232" t="inlineStr">
@@ -32929,12 +32929,12 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -32960,24 +32960,24 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F233" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -33024,10 +33024,10 @@
         <v>0</v>
       </c>
       <c r="W233" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X233" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y233" t="n">
         <v>0</v>
@@ -33036,7 +33036,7 @@
         <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB233" t="n">
         <v>5</v>
@@ -33044,12 +33044,12 @@
       <c r="AC233" t="inlineStr"/>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="AG233" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH233" t="inlineStr">
@@ -33069,12 +33069,12 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -33100,24 +33100,24 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F234" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L234" t="n">
@@ -33164,10 +33164,10 @@
         <v>0</v>
       </c>
       <c r="W234" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X234" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y234" t="n">
         <v>0</v>
@@ -33176,7 +33176,7 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB234" t="n">
         <v>5</v>
@@ -33184,12 +33184,12 @@
       <c r="AC234" t="inlineStr"/>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -33199,22 +33199,22 @@
       </c>
       <c r="AG234" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>01/10/2026 13:31:27</t>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>
@@ -33262,16 +33262,16 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L235" t="n">
-        <v>37255127.79</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -33280,34 +33280,34 @@
         <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>37249300.96</v>
+        <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>8356750.31</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>51957329.92</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>41383303.35</v>
+        <v>0</v>
       </c>
       <c r="T235" t="n">
-        <v>42996067.51</v>
+        <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>43600579.61</v>
+        <v>0</v>
       </c>
       <c r="V235" t="n">
-        <v>1612764.16</v>
+        <v>0</v>
       </c>
       <c r="W235" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X235" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y235" t="n">
         <v>0</v>
@@ -33316,7 +33316,7 @@
         <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB235" t="n">
         <v>5</v>
@@ -33334,27 +33334,167 @@
       </c>
       <c r="AF235" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:51:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>422</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>37865792.79</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>37249300.96</v>
+      </c>
+      <c r="P236" t="n">
+        <v>8356750.31</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>52109942.64</v>
+      </c>
+      <c r="S236" t="n">
+        <v>41383303.35</v>
+      </c>
+      <c r="T236" t="n">
+        <v>42996067.51</v>
+      </c>
+      <c r="U236" t="n">
+        <v>43753192.33</v>
+      </c>
+      <c r="V236" t="n">
+        <v>1612764.16</v>
+      </c>
+      <c r="W236" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X236" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG235" t="inlineStr">
+      <c r="AG236" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH235" t="inlineStr">
+      <c r="AH236" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI235" t="inlineStr">
+      <c r="AI236" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>01/10/2026 13:31:27</t>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:51:01</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5068732.62</v>
+        <v>5163175.62</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5480073.8</v>
+        <v>5627059.5</v>
       </c>
       <c r="P10" t="n">
         <v>9311752.550000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>97816.95</v>
+        <v>99808.71000000001</v>
       </c>
       <c r="S17" t="n">
         <v>71840.72</v>
@@ -2778,7 +2778,7 @@
         <v>71840.72</v>
       </c>
       <c r="U17" t="n">
-        <v>83926.37</v>
+        <v>85918.13</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>600000</v>
       </c>
       <c r="O20" t="n">
-        <v>3509598.53</v>
+        <v>4054085.21</v>
       </c>
       <c r="P20" t="n">
         <v>4557916.3</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
         <v>202693</v>
       </c>
       <c r="O28" t="n">
-        <v>164249.32</v>
+        <v>244813.39</v>
       </c>
       <c r="P28" t="n">
         <v>141816.38</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1307954.61</v>
+        <v>1308912.66</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1306728.76</v>
+        <v>1307954.61</v>
       </c>
       <c r="P30" t="n">
         <v>692092.37</v>
@@ -4589,7 +4589,7 @@
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2793005.27</v>
+        <v>2793134.13</v>
       </c>
       <c r="S30" t="n">
         <v>1923214.84</v>
@@ -4598,7 +4598,7 @@
         <v>2082211.62</v>
       </c>
       <c r="U30" t="n">
-        <v>2100912.9</v>
+        <v>2101041.76</v>
       </c>
       <c r="V30" t="n">
         <v>158996.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>11060881.48</v>
+        <v>11535258.03</v>
       </c>
       <c r="P32" t="n">
         <v>6155204.1</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3093180.1</v>
+        <v>3125989.95</v>
       </c>
       <c r="P46" t="n">
         <v>21943357.71</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7663,25 +7663,25 @@
         <v>7363410.03</v>
       </c>
       <c r="P52" t="n">
-        <v>4937905.31</v>
+        <v>5913951.99</v>
       </c>
       <c r="Q52" t="n">
         <v>278000</v>
       </c>
       <c r="R52" t="n">
-        <v>13892639.52</v>
+        <v>14868686.2</v>
       </c>
       <c r="S52" t="n">
-        <v>8943855.66</v>
+        <v>8777361.949999999</v>
       </c>
       <c r="T52" t="n">
-        <v>11946013.18</v>
+        <v>12922059.86</v>
       </c>
       <c r="U52" t="n">
         <v>8954734.210000001</v>
       </c>
       <c r="V52" t="n">
-        <v>3002157.52</v>
+        <v>4144697.91</v>
       </c>
       <c r="W52" t="n">
         <v>8954734.210000001</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
         <v>1191556.45</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q88" t="n">
         <v>563899.45</v>
@@ -12712,13 +12712,13 @@
         <v>1199605.45</v>
       </c>
       <c r="S88" t="n">
-        <v>1191556.45</v>
+        <v>1199605.4</v>
       </c>
       <c r="T88" t="n">
-        <v>1191556.45</v>
+        <v>1199605.4</v>
       </c>
       <c r="U88" t="n">
-        <v>1199605.45</v>
+        <v>1199605.4</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
         <v>100000</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1432058.79</v>
+        <v>1909411.72</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>114466.75</v>
+        <v>130683.3</v>
       </c>
       <c r="P109" t="n">
         <v>260024.05</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>7688.37</v>
+        <v>7985.91</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
         <v>150000</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
         <v>130000</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22223,22 +22223,22 @@
         <v>9563715.24</v>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>399244</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>10451948</v>
+        <v>10851191.49</v>
       </c>
       <c r="S156" t="n">
-        <v>10052704</v>
+        <v>10451947.49</v>
       </c>
       <c r="T156" t="n">
-        <v>10052704</v>
+        <v>10451947.49</v>
       </c>
       <c r="U156" t="n">
-        <v>10451948</v>
+        <v>10451947.49</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22503,13 +22503,13 @@
         <v>2499846.64</v>
       </c>
       <c r="P158" t="n">
-        <v>16674823.21</v>
+        <v>16697048.4</v>
       </c>
       <c r="Q158" t="n">
         <v>65000</v>
       </c>
       <c r="R158" t="n">
-        <v>23880736.73</v>
+        <v>23925187.11</v>
       </c>
       <c r="S158" t="n">
         <v>2745814.21</v>
@@ -22518,7 +22518,7 @@
         <v>2756814.21</v>
       </c>
       <c r="U158" t="n">
-        <v>7205913.52</v>
+        <v>7228138.71</v>
       </c>
       <c r="V158" t="n">
         <v>11000</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
         <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>46040.84</v>
+        <v>46107.45</v>
       </c>
       <c r="P160" t="n">
         <v>240000</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23200,7 +23200,7 @@
         <v>190000</v>
       </c>
       <c r="O163" t="n">
-        <v>237363.41</v>
+        <v>271122.52</v>
       </c>
       <c r="P163" t="n">
         <v>350343.49</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23331,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>30630.96</v>
+        <v>31523.58</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1772047.84</v>
+        <v>1773211.54</v>
       </c>
       <c r="P170" t="n">
         <v>3439489.73</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26271,7 +26271,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>24545612.47</v>
+        <v>24837570.18</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27683,19 +27683,19 @@
         <v>24545612.47</v>
       </c>
       <c r="P195" t="n">
-        <v>5412701.99</v>
+        <v>5599952.69</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>36334268.46</v>
+        <v>36521519.16</v>
       </c>
       <c r="S195" t="n">
-        <v>29716613.12</v>
+        <v>29779030.02</v>
       </c>
       <c r="T195" t="n">
-        <v>30650929.58</v>
+        <v>30713346.48</v>
       </c>
       <c r="U195" t="n">
         <v>30921566.47</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>95912.85000000001</v>
+        <v>97412.85000000001</v>
       </c>
       <c r="P197" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1625643.01</v>
+        <v>1682929.47</v>
       </c>
       <c r="P199" t="n">
         <v>2763223.97</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29780,7 +29780,7 @@
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>318270.87</v>
+        <v>318485.12</v>
       </c>
       <c r="P210" t="n">
         <v>4837262.97</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30191,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>31100</v>
+        <v>31800</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>83680665.70999999</v>
+        <v>86108915.70999999</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -32303,7 +32303,7 @@
         <v>79306283.70999999</v>
       </c>
       <c r="P228" t="n">
-        <v>80527720</v>
+        <v>88356395.75</v>
       </c>
       <c r="Q228" t="n">
         <v>4727853</v>
@@ -32318,7 +32318,7 @@
         <v>121904379.2</v>
       </c>
       <c r="U228" t="n">
-        <v>136889022</v>
+        <v>129060346.25</v>
       </c>
       <c r="V228" t="n">
         <v>0</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>62279940.24</v>
+        <v>62528122.08</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>61551749.34</v>
+        <v>61731749.34</v>
       </c>
       <c r="P229" t="n">
         <v>51388595.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>37865792.79</v>
+        <v>38438022.79</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -33420,10 +33420,10 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>37249300.96</v>
+        <v>37255127.79</v>
       </c>
       <c r="P236" t="n">
-        <v>8356750.31</v>
+        <v>8468714.279999999</v>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
@@ -33432,13 +33432,13 @@
         <v>52109942.64</v>
       </c>
       <c r="S236" t="n">
-        <v>41383303.35</v>
+        <v>41414418.49</v>
       </c>
       <c r="T236" t="n">
-        <v>42996067.51</v>
+        <v>43027182.65</v>
       </c>
       <c r="U236" t="n">
-        <v>43753192.33</v>
+        <v>43641228.36</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>02/10/2026 12:51:01</t>
+          <t>05/10/2026 15:29:21</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>219675.41</v>
+        <v>222325.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>200936.59</v>
       </c>
       <c r="P9" t="n">
-        <v>388846.6</v>
+        <v>558517.84</v>
       </c>
       <c r="Q9" t="n">
         <v>128044</v>
       </c>
       <c r="R9" t="n">
-        <v>874689.4</v>
+        <v>1044360.64</v>
       </c>
       <c r="S9" t="n">
         <v>312411.09</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>182179.94</v>
+        <v>186539.94</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4592,10 +4592,10 @@
         <v>2793134.13</v>
       </c>
       <c r="S30" t="n">
-        <v>1923214.84</v>
+        <v>1923343.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2082211.62</v>
+        <v>2082340.48</v>
       </c>
       <c r="U30" t="n">
         <v>2101041.76</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4723,13 +4723,13 @@
         <v>3141258.4</v>
       </c>
       <c r="P31" t="n">
-        <v>7011787.82</v>
+        <v>9202815.26</v>
       </c>
       <c r="Q31" t="n">
         <v>36087</v>
       </c>
       <c r="R31" t="n">
-        <v>14215932.82</v>
+        <v>16406960.26</v>
       </c>
       <c r="S31" t="n">
         <v>4889325.07</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3156507.76</v>
+        <v>3157303.15</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -7803,13 +7803,13 @@
         <v>155252.3</v>
       </c>
       <c r="P53" t="n">
-        <v>163921.91</v>
+        <v>201637.53</v>
       </c>
       <c r="Q53" t="n">
         <v>43369</v>
       </c>
       <c r="R53" t="n">
-        <v>674236.8</v>
+        <v>711952.42</v>
       </c>
       <c r="S53" t="n">
         <v>293450.04</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16623,13 +16623,13 @@
         <v>45683.89</v>
       </c>
       <c r="P116" t="n">
-        <v>120156.43</v>
+        <v>223741.58</v>
       </c>
       <c r="Q116" t="n">
         <v>19083</v>
       </c>
       <c r="R116" t="n">
-        <v>343067.4</v>
+        <v>446652.55</v>
       </c>
       <c r="S116" t="n">
         <v>114478.54</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>15406.2</v>
+        <v>17189.2</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23063,13 +23063,13 @@
         <v>200936.19</v>
       </c>
       <c r="P162" t="n">
-        <v>189359.94</v>
+        <v>309378.12</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>745790.8</v>
+        <v>865808.98</v>
       </c>
       <c r="S162" t="n">
         <v>339569.01</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>136238.21</v>
+        <v>151528.37</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -26849,7 +26849,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -26858,7 +26858,7 @@
         <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27692,10 +27692,10 @@
         <v>36521519.16</v>
       </c>
       <c r="S195" t="n">
-        <v>29779030.02</v>
+        <v>30126000.12</v>
       </c>
       <c r="T195" t="n">
-        <v>30713346.48</v>
+        <v>31060316.58</v>
       </c>
       <c r="U195" t="n">
         <v>30921566.47</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>90884.2</v>
+        <v>91772.2</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28103,13 +28103,13 @@
         <v>869016.0600000001</v>
       </c>
       <c r="P198" t="n">
-        <v>1760683.97</v>
+        <v>2614040.51</v>
       </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>4263497.9</v>
+        <v>5116854.44</v>
       </c>
       <c r="S198" t="n">
         <v>1620855.47</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>05/10/2026 15:29:21</t>
+          <t>06/10/2026 12:59:04</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>1132677.56</v>
       </c>
       <c r="S7" t="n">
-        <v>460484.87</v>
+        <v>518742.47</v>
       </c>
       <c r="T7" t="n">
-        <v>565484.87</v>
+        <v>623742.47</v>
       </c>
       <c r="U7" t="n">
         <v>648160.5699999999</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>165966</v>
       </c>
       <c r="O8" t="n">
-        <v>135667.54</v>
+        <v>142145.4</v>
       </c>
       <c r="P8" t="n">
         <v>272020.19</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1652,10 +1652,10 @@
         <v>1044360.64</v>
       </c>
       <c r="S9" t="n">
-        <v>312411.09</v>
+        <v>482082.33</v>
       </c>
       <c r="T9" t="n">
-        <v>312411.09</v>
+        <v>482082.33</v>
       </c>
       <c r="U9" t="n">
         <v>485842.8</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5627059.5</v>
+        <v>5715832.79</v>
       </c>
       <c r="P10" t="n">
         <v>9311752.550000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3752,10 +3752,10 @@
         <v>131343.68</v>
       </c>
       <c r="S24" t="n">
-        <v>10960.6</v>
+        <v>40960.6</v>
       </c>
       <c r="T24" t="n">
-        <v>10960.6</v>
+        <v>40960.6</v>
       </c>
       <c r="U24" t="n">
         <v>62879.62</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4732,10 +4732,10 @@
         <v>16406960.26</v>
       </c>
       <c r="S31" t="n">
-        <v>4889325.07</v>
+        <v>7080352.51</v>
       </c>
       <c r="T31" t="n">
-        <v>4889325.07</v>
+        <v>7080352.51</v>
       </c>
       <c r="U31" t="n">
         <v>7204145</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4869,16 +4869,16 @@
         <v>103049</v>
       </c>
       <c r="R32" t="n">
-        <v>24832306.47</v>
+        <v>26432306.47</v>
       </c>
       <c r="S32" t="n">
-        <v>18489264.06</v>
+        <v>19903484.38</v>
       </c>
       <c r="T32" t="n">
-        <v>22274228.47</v>
+        <v>23688448.79</v>
       </c>
       <c r="U32" t="n">
-        <v>18677102.37</v>
+        <v>20277102.37</v>
       </c>
       <c r="V32" t="n">
         <v>3784964.41</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>528275.5699999999</v>
+        <v>530007.8</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3157303.15</v>
+        <v>3222202.26</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -7812,10 +7812,10 @@
         <v>711952.42</v>
       </c>
       <c r="S53" t="n">
-        <v>293450.04</v>
+        <v>331165.66</v>
       </c>
       <c r="T53" t="n">
-        <v>293450.04</v>
+        <v>331165.66</v>
       </c>
       <c r="U53" t="n">
         <v>510314.89</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16632,10 +16632,10 @@
         <v>446652.55</v>
       </c>
       <c r="S116" t="n">
-        <v>114478.54</v>
+        <v>218063.69</v>
       </c>
       <c r="T116" t="n">
-        <v>114478.54</v>
+        <v>218063.69</v>
       </c>
       <c r="U116" t="n">
         <v>222910.97</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="S123" t="n">
         <v>300000</v>
@@ -17618,7 +17618,7 @@
         <v>300000</v>
       </c>
       <c r="U123" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20120,7 +20120,7 @@
         <v>270000</v>
       </c>
       <c r="O141" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>2499846.64</v>
+        <v>2504846.64</v>
       </c>
       <c r="P158" t="n">
         <v>16697048.4</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23072,10 +23072,10 @@
         <v>865808.98</v>
       </c>
       <c r="S162" t="n">
-        <v>339569.01</v>
+        <v>459587.19</v>
       </c>
       <c r="T162" t="n">
-        <v>339569.01</v>
+        <v>459587.19</v>
       </c>
       <c r="U162" t="n">
         <v>556430.86</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1923344.33</v>
+        <v>1974390.7</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1773211.54</v>
+        <v>1807295.56</v>
       </c>
       <c r="P170" t="n">
         <v>3439489.73</v>
@@ -24192,10 +24192,10 @@
         <v>6659918.53</v>
       </c>
       <c r="S170" t="n">
-        <v>3004466.42</v>
+        <v>3028966.42</v>
       </c>
       <c r="T170" t="n">
-        <v>3148109.3</v>
+        <v>3172609.3</v>
       </c>
       <c r="U170" t="n">
         <v>3220428.8</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>7935600</v>
+        <v>7919200</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -27540,7 +27540,7 @@
         <v>960000</v>
       </c>
       <c r="O194" t="n">
-        <v>7107600</v>
+        <v>7091200</v>
       </c>
       <c r="P194" t="n">
         <v>0</v>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28112,10 +28112,10 @@
         <v>5116854.44</v>
       </c>
       <c r="S198" t="n">
-        <v>1620855.47</v>
+        <v>2474212.01</v>
       </c>
       <c r="T198" t="n">
-        <v>1687781.31</v>
+        <v>2541137.85</v>
       </c>
       <c r="U198" t="n">
         <v>2502813.93</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1682929.47</v>
+        <v>1709187.91</v>
       </c>
       <c r="P199" t="n">
         <v>2763223.97</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>86108915.70999999</v>
+        <v>88643125.70999999</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>62528122.08</v>
+        <v>62618122.08</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>
@@ -33432,10 +33432,10 @@
         <v>52109942.64</v>
       </c>
       <c r="S236" t="n">
-        <v>41414418.49</v>
+        <v>41651440.49</v>
       </c>
       <c r="T236" t="n">
-        <v>43027182.65</v>
+        <v>43264204.65</v>
       </c>
       <c r="U236" t="n">
         <v>43641228.36</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>06/10/2026 12:59:04</t>
+          <t>07/10/2026 13:32:25</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1360,16 +1360,16 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>182520.41</v>
+        <v>184675.41</v>
       </c>
       <c r="P7" t="n">
-        <v>484516.99</v>
+        <v>510399.27</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>1132677.56</v>
+        <v>1159131.48</v>
       </c>
       <c r="S7" t="n">
         <v>518742.47</v>
@@ -1378,7 +1378,7 @@
         <v>623742.47</v>
       </c>
       <c r="U7" t="n">
-        <v>648160.5699999999</v>
+        <v>648732.21</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>142345.15</v>
+        <v>148595.06</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1503,25 +1503,25 @@
         <v>142145.4</v>
       </c>
       <c r="P8" t="n">
-        <v>272020.19</v>
+        <v>287106.31</v>
       </c>
       <c r="Q8" t="n">
         <v>57913</v>
       </c>
       <c r="R8" t="n">
-        <v>687985.6899999999</v>
+        <v>753072.3100000001</v>
       </c>
       <c r="S8" t="n">
-        <v>414316.36</v>
+        <v>464316.86</v>
       </c>
       <c r="T8" t="n">
-        <v>476583.54</v>
+        <v>540021.02</v>
       </c>
       <c r="U8" t="n">
-        <v>415965.5</v>
+        <v>465966</v>
       </c>
       <c r="V8" t="n">
-        <v>62267.18</v>
+        <v>75704.16</v>
       </c>
       <c r="W8" t="n">
         <v>465966</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5767135.47</v>
+        <v>5957726.68</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,25 +1780,25 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5715832.79</v>
+        <v>5728532.94</v>
       </c>
       <c r="P10" t="n">
-        <v>9311752.550000001</v>
+        <v>9379886.16</v>
       </c>
       <c r="Q10" t="n">
         <v>3127008</v>
       </c>
       <c r="R10" t="n">
-        <v>21860351.03</v>
+        <v>21941159.34</v>
       </c>
       <c r="S10" t="n">
-        <v>11231157.78</v>
+        <v>11345647.03</v>
       </c>
       <c r="T10" t="n">
-        <v>12825228.45</v>
+        <v>12939717.7</v>
       </c>
       <c r="U10" t="n">
-        <v>12548598.48</v>
+        <v>12561273.18</v>
       </c>
       <c r="V10" t="n">
         <v>1594070.67</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>209678.86</v>
+        <v>223265.62</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>208352.16</v>
+        <v>208502.16</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2763,13 +2763,13 @@
         <v>69900.72</v>
       </c>
       <c r="P17" t="n">
-        <v>13890.58</v>
+        <v>16525.7</v>
       </c>
       <c r="Q17" t="n">
         <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>99808.71000000001</v>
+        <v>102443.83</v>
       </c>
       <c r="S17" t="n">
         <v>71840.72</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4054085.21</v>
+        <v>4067379.62</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         <v>4054085.21</v>
       </c>
       <c r="P20" t="n">
-        <v>4557916.3</v>
+        <v>5038787.84</v>
       </c>
       <c r="Q20" t="n">
         <v>1075689</v>
       </c>
       <c r="R20" t="n">
-        <v>11165460.19</v>
+        <v>11646331.7</v>
       </c>
       <c r="S20" t="n">
         <v>5982058.26</v>
@@ -3198,7 +3198,7 @@
         <v>6351244.21</v>
       </c>
       <c r="U20" t="n">
-        <v>6607543.89</v>
+        <v>6607543.86</v>
       </c>
       <c r="V20" t="n">
         <v>369185.95</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1440</v>
+        <v>6360</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3743,13 +3743,13 @@
         <v>1440</v>
       </c>
       <c r="P24" t="n">
-        <v>68464.06</v>
+        <v>90383.08</v>
       </c>
       <c r="Q24" t="n">
         <v>169694</v>
       </c>
       <c r="R24" t="n">
-        <v>131343.68</v>
+        <v>153262.7</v>
       </c>
       <c r="S24" t="n">
         <v>40960.6</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
         <v>202693</v>
       </c>
       <c r="O28" t="n">
-        <v>244813.39</v>
+        <v>255571.15</v>
       </c>
       <c r="P28" t="n">
         <v>141816.38</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1308912.66</v>
+        <v>1395790.06</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11564529.15</v>
+        <v>11588751.93</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,10 +4860,10 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>11535258.03</v>
+        <v>11564529.15</v>
       </c>
       <c r="P32" t="n">
-        <v>6155204.1</v>
+        <v>6186537.4</v>
       </c>
       <c r="Q32" t="n">
         <v>103049</v>
@@ -4878,7 +4878,7 @@
         <v>23688448.79</v>
       </c>
       <c r="U32" t="n">
-        <v>20277102.37</v>
+        <v>20245769.07</v>
       </c>
       <c r="V32" t="n">
         <v>3784964.41</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>523154.14</v>
+        <v>527764.12</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2164294.85</v>
+        <v>2166113.85</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2164294.85</v>
+        <v>2164643.14</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5429,16 +5429,16 @@
         <v>14953</v>
       </c>
       <c r="R36" t="n">
-        <v>5916961.44</v>
+        <v>6516961.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2983887.66</v>
+        <v>3583887.66</v>
       </c>
       <c r="T36" t="n">
-        <v>3012141.62</v>
+        <v>3612141.62</v>
       </c>
       <c r="U36" t="n">
-        <v>2985047</v>
+        <v>3585047</v>
       </c>
       <c r="V36" t="n">
         <v>28253.96</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6403,19 +6403,19 @@
         <v>10641.28</v>
       </c>
       <c r="P43" t="n">
-        <v>169485.85</v>
+        <v>173078.25</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>349093.17</v>
+        <v>352685.57</v>
       </c>
       <c r="S43" t="n">
-        <v>119213.37</v>
+        <v>123413.37</v>
       </c>
       <c r="T43" t="n">
-        <v>123149.37</v>
+        <v>127349.37</v>
       </c>
       <c r="U43" t="n">
         <v>179607.32</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6543,13 +6543,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>96992.57000000001</v>
+        <v>115451.9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246992.57</v>
+        <v>265451.9</v>
       </c>
       <c r="S44" t="n">
         <v>72380.13</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>1006324.68</v>
       </c>
       <c r="O45" t="n">
-        <v>825646.38</v>
+        <v>944859.7</v>
       </c>
       <c r="P45" t="n">
         <v>1473433.88</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3222202.26</v>
+        <v>3248682.93</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3125989.95</v>
+        <v>3142388.85</v>
       </c>
       <c r="P46" t="n">
         <v>21943357.71</v>
@@ -6832,10 +6832,10 @@
         <v>31629816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>5977842.74</v>
+        <v>6005553.51</v>
       </c>
       <c r="T46" t="n">
-        <v>6478292.3</v>
+        <v>6506003.07</v>
       </c>
       <c r="U46" t="n">
         <v>9686458.939999999</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184161.59</v>
+        <v>198540.72</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7651,16 +7651,16 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>8777361.949999999</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
         <v>7612695.77</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>7363410.03</v>
       </c>
       <c r="P52" t="n">
         <v>5913951.99</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8232,10 +8232,10 @@
         <v>130000</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="U56" t="n">
         <v>130000</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8643,13 +8643,13 @@
         <v>8643538.5</v>
       </c>
       <c r="P59" t="n">
-        <v>7507405.83</v>
+        <v>7511479.83</v>
       </c>
       <c r="Q59" t="n">
         <v>4186869</v>
       </c>
       <c r="R59" t="n">
-        <v>25835164.83</v>
+        <v>25839238.83</v>
       </c>
       <c r="S59" t="n">
         <v>18060730.63</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="AB74" t="n">
         <v>5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="O84" t="n">
         <v>80000</v>
@@ -12164,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="AB84" t="n">
         <v>5</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1191556.45</v>
+        <v>1199605.4</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -12983,13 +12983,13 @@
         <v>657979.71</v>
       </c>
       <c r="P90" t="n">
-        <v>953387.74</v>
+        <v>956845.74</v>
       </c>
       <c r="Q90" t="n">
         <v>827817</v>
       </c>
       <c r="R90" t="n">
-        <v>2884872.14</v>
+        <v>2888330.14</v>
       </c>
       <c r="S90" t="n">
         <v>1928026.4</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
         <v>1432058.79</v>
       </c>
       <c r="P106" t="n">
-        <v>238607.79</v>
+        <v>238608</v>
       </c>
       <c r="Q106" t="n">
         <v>478393</v>
@@ -15238,7 +15238,7 @@
         <v>2269051.27</v>
       </c>
       <c r="U106" t="n">
-        <v>1909411.93</v>
+        <v>1909411.72</v>
       </c>
       <c r="V106" t="n">
         <v>359639.55</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15360,16 +15360,16 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>16057.01</v>
+        <v>16574.21</v>
       </c>
       <c r="P107" t="n">
-        <v>1235.82</v>
+        <v>1830.41</v>
       </c>
       <c r="Q107" t="n">
         <v>30045</v>
       </c>
       <c r="R107" t="n">
-        <v>106235.82</v>
+        <v>106830.41</v>
       </c>
       <c r="S107" t="n">
         <v>88523.00999999999</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>286730.01</v>
+        <v>317782.4</v>
       </c>
       <c r="P108" t="n">
         <v>150685.93</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>7985.91</v>
+        <v>8342.23</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         <v>1690301.29</v>
       </c>
       <c r="P114" t="n">
-        <v>8049.6</v>
+        <v>10732.8</v>
       </c>
       <c r="Q114" t="n">
         <v>268051</v>
@@ -16352,13 +16352,13 @@
         <v>2198630.56</v>
       </c>
       <c r="S114" t="n">
-        <v>2027342.68</v>
+        <v>2032709.08</v>
       </c>
       <c r="T114" t="n">
-        <v>2027342.68</v>
+        <v>2032709.08</v>
       </c>
       <c r="U114" t="n">
-        <v>2190580.96</v>
+        <v>2187897.76</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16760,16 +16760,16 @@
         <v>30000</v>
       </c>
       <c r="O117" t="n">
-        <v>184781.14</v>
+        <v>212807.32</v>
       </c>
       <c r="P117" t="n">
-        <v>50000</v>
+        <v>53742.53</v>
       </c>
       <c r="Q117" t="n">
         <v>57248</v>
       </c>
       <c r="R117" t="n">
-        <v>442635.02</v>
+        <v>446377.55</v>
       </c>
       <c r="S117" t="n">
         <v>363452.83</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18023,13 +18023,13 @@
         <v>75642</v>
       </c>
       <c r="P126" t="n">
-        <v>321.81</v>
+        <v>1599.29</v>
       </c>
       <c r="Q126" t="n">
         <v>98942</v>
       </c>
       <c r="R126" t="n">
-        <v>172841.29</v>
+        <v>175241.29</v>
       </c>
       <c r="S126" t="n">
         <v>85742</v>
@@ -18038,7 +18038,7 @@
         <v>85742</v>
       </c>
       <c r="U126" t="n">
-        <v>172519.48</v>
+        <v>173642</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>8034136.5</v>
+        <v>8044178.59</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22363,13 +22363,13 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>19046</v>
+        <v>19646</v>
       </c>
       <c r="Q157" t="n">
         <v>24738</v>
       </c>
       <c r="R157" t="n">
-        <v>39246</v>
+        <v>39846</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22503,13 +22503,13 @@
         <v>2504846.64</v>
       </c>
       <c r="P158" t="n">
-        <v>16697048.4</v>
+        <v>16780694.9</v>
       </c>
       <c r="Q158" t="n">
         <v>65000</v>
       </c>
       <c r="R158" t="n">
-        <v>23925187.11</v>
+        <v>23928833.61</v>
       </c>
       <c r="S158" t="n">
         <v>2745814.21</v>
@@ -22518,7 +22518,7 @@
         <v>2756814.21</v>
       </c>
       <c r="U158" t="n">
-        <v>7228138.71</v>
+        <v>7148138.71</v>
       </c>
       <c r="V158" t="n">
         <v>11000</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -22923,13 +22923,13 @@
         <v>15406.2</v>
       </c>
       <c r="P161" t="n">
-        <v>67000</v>
+        <v>69239.35000000001</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>107627.35</v>
+        <v>109866.7</v>
       </c>
       <c r="S161" t="n">
         <v>18388</v>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>30603.28</v>
+        <v>30678.28</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>151528.37</v>
+        <v>152184.37</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24040,7 @@
         <v>564000</v>
       </c>
       <c r="O169" t="n">
-        <v>566909.84</v>
+        <v>647896.96</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24180,16 +24180,16 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1807295.56</v>
+        <v>1921295.56</v>
       </c>
       <c r="P170" t="n">
-        <v>3439489.73</v>
+        <v>3510552.61</v>
       </c>
       <c r="Q170" t="n">
         <v>324976</v>
       </c>
       <c r="R170" t="n">
-        <v>6659918.53</v>
+        <v>6730981.41</v>
       </c>
       <c r="S170" t="n">
         <v>3028966.42</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24320,7 +24320,7 @@
         <v>158000</v>
       </c>
       <c r="O171" t="n">
-        <v>147652.91</v>
+        <v>174187.05</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25717,7 +25717,7 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>0</v>
       </c>
       <c r="W181" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X181" t="n">
         <v>0</v>
@@ -25756,7 +25756,7 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="AB181" t="n">
         <v>5</v>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26837,7 +26837,7 @@
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>475000</v>
+        <v>675000</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -26864,7 +26864,7 @@
         <v>0</v>
       </c>
       <c r="W189" t="n">
-        <v>475000</v>
+        <v>675000</v>
       </c>
       <c r="X189" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>475000</v>
+        <v>675000</v>
       </c>
       <c r="AB189" t="n">
         <v>5</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -26980,7 +26980,7 @@
         <v>261000</v>
       </c>
       <c r="O190" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="P190" t="n">
         <v>0</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27540,16 +27540,16 @@
         <v>960000</v>
       </c>
       <c r="O194" t="n">
-        <v>7091200</v>
+        <v>7919200</v>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1140039.67</v>
       </c>
       <c r="Q194" t="n">
         <v>1421600</v>
       </c>
       <c r="R194" t="n">
-        <v>9076439.67</v>
+        <v>10781639.67</v>
       </c>
       <c r="S194" t="n">
         <v>7935600</v>
@@ -27558,7 +27558,7 @@
         <v>8889200</v>
       </c>
       <c r="U194" t="n">
-        <v>9076439.67</v>
+        <v>9641600</v>
       </c>
       <c r="V194" t="n">
         <v>953600</v>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>24837570.18</v>
+        <v>27454785.08</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -27820,16 +27820,16 @@
         <v>52998</v>
       </c>
       <c r="O196" t="n">
-        <v>89160.2</v>
+        <v>90884.2</v>
       </c>
       <c r="P196" t="n">
-        <v>66171.82000000001</v>
+        <v>67022.03</v>
       </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>267909.15</v>
+        <v>268759.36</v>
       </c>
       <c r="S196" t="n">
         <v>161394.12</v>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>869016.0600000001</v>
+        <v>898725.67</v>
       </c>
       <c r="P198" t="n">
         <v>2614040.51</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1709187.91</v>
+        <v>1736975.36</v>
       </c>
       <c r="P199" t="n">
         <v>2763223.97</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29503,13 +29503,13 @@
         <v>9864</v>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>127.8</v>
       </c>
       <c r="Q208" t="n">
         <v>4626</v>
       </c>
       <c r="R208" t="n">
-        <v>9991.799999999999</v>
+        <v>10127.8</v>
       </c>
       <c r="S208" t="n">
         <v>9864</v>
@@ -29518,7 +29518,7 @@
         <v>9864</v>
       </c>
       <c r="U208" t="n">
-        <v>9991.799999999999</v>
+        <v>10000</v>
       </c>
       <c r="V208" t="n">
         <v>0</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29780,16 +29780,16 @@
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>318485.12</v>
+        <v>356543.33</v>
       </c>
       <c r="P210" t="n">
-        <v>4837262.97</v>
+        <v>4909802.89</v>
       </c>
       <c r="Q210" t="n">
         <v>5886824</v>
       </c>
       <c r="R210" t="n">
-        <v>7758858.94</v>
+        <v>7831398.86</v>
       </c>
       <c r="S210" t="n">
         <v>559609.14</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30191,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>31800</v>
+        <v>36000</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30629,7 +30629,7 @@
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="V216" t="n">
         <v>0</v>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -31871,40 +31871,40 @@
         </is>
       </c>
       <c r="L225" t="n">
+        <v>146651466.23</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>7828675.75</v>
+      </c>
+      <c r="O225" t="n">
         <v>145445519.3</v>
       </c>
-      <c r="M225" t="n">
-        <v>0</v>
-      </c>
-      <c r="N225" t="n">
-        <v>0</v>
-      </c>
-      <c r="O225" t="n">
-        <v>143327924.45</v>
-      </c>
       <c r="P225" t="n">
-        <v>50520982.11</v>
+        <v>51023116.8</v>
       </c>
       <c r="Q225" t="n">
         <v>5735947</v>
       </c>
       <c r="R225" t="n">
-        <v>216235104.06</v>
+        <v>224565914.38</v>
       </c>
       <c r="S225" t="n">
-        <v>164527540.7</v>
+        <v>165211987.28</v>
       </c>
       <c r="T225" t="n">
-        <v>170802298.36</v>
+        <v>171550415.91</v>
       </c>
       <c r="U225" t="n">
-        <v>165714121.95</v>
+        <v>173542797.58</v>
       </c>
       <c r="V225" t="n">
-        <v>6274757.66</v>
+        <v>6338428.63</v>
       </c>
       <c r="W225" t="n">
-        <v>165715582</v>
+        <v>173544257.75</v>
       </c>
       <c r="X225" t="n">
         <v>171813039</v>
@@ -31916,7 +31916,7 @@
         <v>6097457</v>
       </c>
       <c r="AA225" t="n">
-        <v>165715582</v>
+        <v>173544257.75</v>
       </c>
       <c r="AB225" t="n">
         <v>5</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32300,7 +32300,7 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>79306283.70999999</v>
+        <v>81734533.70999999</v>
       </c>
       <c r="P228" t="n">
         <v>88356395.75</v>
@@ -32324,7 +32324,7 @@
         <v>0</v>
       </c>
       <c r="W228" t="n">
-        <v>136889022</v>
+        <v>129060346.25</v>
       </c>
       <c r="X228" t="n">
         <v>141616875</v>
@@ -32333,10 +32333,10 @@
         <v>4727853</v>
       </c>
       <c r="Z228" t="n">
-        <v>4727853</v>
+        <v>12556528.75</v>
       </c>
       <c r="AA228" t="n">
-        <v>136889022</v>
+        <v>129060346.25</v>
       </c>
       <c r="AB228" t="n">
         <v>5</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>61731749.34</v>
+        <v>62065695.96</v>
       </c>
       <c r="P229" t="n">
         <v>51388595.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32711,7 +32711,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>907561.39</v>
+        <v>1023951.79</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>38438022.79</v>
+        <v>38845761.79</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -33423,7 +33423,7 @@
         <v>37255127.79</v>
       </c>
       <c r="P236" t="n">
-        <v>8468714.279999999</v>
+        <v>8715032.83</v>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
@@ -33438,7 +33438,7 @@
         <v>43264204.65</v>
       </c>
       <c r="U236" t="n">
-        <v>43641228.36</v>
+        <v>43394909.81</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>07/10/2026 13:32:25</t>
+          <t>09/10/2026 13:18:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5068732.62</v>
+        <v>5163175.62</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>1159131.48</v>
       </c>
       <c r="S7" t="n">
-        <v>518742.47</v>
+        <v>534944.47</v>
       </c>
       <c r="T7" t="n">
-        <v>623742.47</v>
+        <v>639944.47</v>
       </c>
       <c r="U7" t="n">
         <v>648732.21</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>148595.06</v>
+        <v>156522.87</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>200936.59</v>
+        <v>253723.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5957726.68</v>
+        <v>6282813.54</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5728532.94</v>
+        <v>5718433.73</v>
       </c>
       <c r="P10" t="n">
-        <v>9379886.16</v>
+        <v>9392219.16</v>
       </c>
       <c r="Q10" t="n">
         <v>3127008</v>
@@ -1792,16 +1792,16 @@
         <v>21941159.34</v>
       </c>
       <c r="S10" t="n">
-        <v>11345647.03</v>
+        <v>11333314.03</v>
       </c>
       <c r="T10" t="n">
         <v>12939717.7</v>
       </c>
       <c r="U10" t="n">
-        <v>12561273.18</v>
+        <v>12548940.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1594070.67</v>
+        <v>1606403.67</v>
       </c>
       <c r="W10" t="n">
         <v>12746699.12</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>69900.72</v>
+        <v>71840.72</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>102443.83</v>
+        <v>301525.7</v>
       </c>
       <c r="S17" t="n">
         <v>71840.72</v>
@@ -2778,7 +2778,7 @@
         <v>71840.72</v>
       </c>
       <c r="U17" t="n">
-        <v>85918.13</v>
+        <v>285000</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1185724.86</v>
+        <v>1335699.33</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1395790.06</v>
+        <v>1452022.14</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1307954.61</v>
+        <v>1308912.66</v>
       </c>
       <c r="P30" t="n">
         <v>692092.37</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4711,16 +4711,16 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3882992.85</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>3151167.44</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3141258.4</v>
       </c>
       <c r="P31" t="n">
         <v>9202815.26</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11588751.93</v>
+        <v>12593674.78</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>530007.8</v>
+        <v>561146.24</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>98254.77</v>
+        <v>112525.09</v>
       </c>
       <c r="P34" t="n">
         <v>226413.89</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2166113.85</v>
+        <v>2167358.25</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2164643.14</v>
+        <v>2166113.85</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6543,13 +6543,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>115451.9</v>
+        <v>117451.9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>265451.9</v>
+        <v>267451.9</v>
       </c>
       <c r="S44" t="n">
         <v>72380.13</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3248682.93</v>
+        <v>3427759.11</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3142388.85</v>
+        <v>3144383.42</v>
       </c>
       <c r="P46" t="n">
         <v>21943357.71</v>
@@ -6829,7 +6829,7 @@
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31629816.65</v>
+        <v>31631816.65</v>
       </c>
       <c r="S46" t="n">
         <v>6005553.51</v>
@@ -6838,7 +6838,7 @@
         <v>6506003.07</v>
       </c>
       <c r="U46" t="n">
-        <v>9686458.939999999</v>
+        <v>9688458.939999999</v>
       </c>
       <c r="V46" t="n">
         <v>500449.56</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>155252.3</v>
+        <v>188253.47</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>24921.65</v>
+        <v>28785.53</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1126850</v>
+        <v>1261700</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -13132,10 +13132,10 @@
         <v>1800000</v>
       </c>
       <c r="S91" t="n">
-        <v>1128400</v>
+        <v>1263250</v>
       </c>
       <c r="T91" t="n">
-        <v>1145450</v>
+        <v>1280300</v>
       </c>
       <c r="U91" t="n">
         <v>1800000</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
         <v>237567.93</v>
       </c>
       <c r="O106" t="n">
-        <v>1432058.79</v>
+        <v>1909411.72</v>
       </c>
       <c r="P106" t="n">
         <v>238608</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>317782.4</v>
+        <v>327691.44</v>
       </c>
       <c r="P108" t="n">
         <v>150685.93</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>45683.89</v>
+        <v>76195</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17600,7 +17600,7 @@
         <v>450000</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
         <v>8445809.92</v>
       </c>
       <c r="P143" t="n">
-        <v>9814403.59</v>
+        <v>10538167</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>8445809.92</v>
       </c>
       <c r="U143" t="n">
-        <v>9169573.33</v>
+        <v>8445809.92</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>8034136.5</v>
+        <v>8044178.59</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>200936.19</v>
+        <v>249508.12</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1974390.7</v>
+        <v>2025437.07</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1921295.56</v>
+        <v>1923344.33</v>
       </c>
       <c r="P170" t="n">
         <v>3510552.61</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26280,7 +26280,7 @@
         <v>230000</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>27454785.08</v>
+        <v>29390686.85</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27680,7 +27680,7 @@
         <v>8495211.470000001</v>
       </c>
       <c r="O195" t="n">
-        <v>24545612.47</v>
+        <v>24837570.18</v>
       </c>
       <c r="P195" t="n">
         <v>5599952.69</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>97412.85000000001</v>
+        <v>108839.25</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28091,16 +28091,16 @@
         </is>
       </c>
       <c r="L198" t="n">
+        <v>1167627.94</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
         <v>908634.71</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" t="n">
-        <v>898725.67</v>
       </c>
       <c r="P198" t="n">
         <v>2614040.51</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1736975.36</v>
+        <v>1763164.64</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>15742.8</v>
+        <v>17710.65</v>
       </c>
       <c r="M201" t="n">
         <v>0</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>31100</v>
+        <v>31800</v>
       </c>
       <c r="P213" t="n">
         <v>11400</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
         <v>5686650.13</v>
       </c>
       <c r="O221" t="n">
-        <v>34668633.7</v>
+        <v>38440789.58</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>62065695.96</v>
+        <v>62245695.96</v>
       </c>
       <c r="P229" t="n">
         <v>51388595.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>38845761.79</v>
+        <v>39113895.79</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -33420,7 +33420,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>37255127.79</v>
+        <v>38438022.79</v>
       </c>
       <c r="P236" t="n">
         <v>8715032.83</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>09/10/2026 13:18:39</t>
+          <t>10/10/2026 12:22:00</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>10/10/2026 12:22:00</t>
+          <t>11/10/2026 12:45:52</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>11/10/2026 12:45:52</t>
+          <t>12/10/2026 16:02:37</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>1159131.48</v>
       </c>
       <c r="S7" t="n">
-        <v>534944.47</v>
+        <v>537319.47</v>
       </c>
       <c r="T7" t="n">
-        <v>639944.47</v>
+        <v>642319.47</v>
       </c>
       <c r="U7" t="n">
         <v>648732.21</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>156522.87</v>
+        <v>160450.48</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6282813.54</v>
+        <v>6326046.26</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,16 +1780,16 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5718433.73</v>
+        <v>5754802.47</v>
       </c>
       <c r="P10" t="n">
-        <v>9392219.16</v>
+        <v>9813569.16</v>
       </c>
       <c r="Q10" t="n">
         <v>3127008</v>
       </c>
       <c r="R10" t="n">
-        <v>21941159.34</v>
+        <v>22490631.25</v>
       </c>
       <c r="S10" t="n">
         <v>11333314.03</v>
@@ -1798,7 +1798,7 @@
         <v>12939717.7</v>
       </c>
       <c r="U10" t="n">
-        <v>12548940.18</v>
+        <v>12677062.09</v>
       </c>
       <c r="V10" t="n">
         <v>1606403.67</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>223265.62</v>
+        <v>224084.87</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4067379.62</v>
+        <v>4068546.28</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1452022.14</v>
+        <v>1460678.1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4583,13 +4583,13 @@
         <v>1308912.66</v>
       </c>
       <c r="P30" t="n">
-        <v>692092.37</v>
+        <v>714645.38</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2793134.13</v>
+        <v>2815687.13</v>
       </c>
       <c r="S30" t="n">
         <v>1923343.7</v>
@@ -4598,7 +4598,7 @@
         <v>2082340.48</v>
       </c>
       <c r="U30" t="n">
-        <v>2101041.76</v>
+        <v>2101041.75</v>
       </c>
       <c r="V30" t="n">
         <v>158996.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12593674.78</v>
+        <v>12692147.91</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>11564529.15</v>
       </c>
       <c r="P32" t="n">
-        <v>6186537.4</v>
+        <v>6186887.32</v>
       </c>
       <c r="Q32" t="n">
         <v>103049</v>
@@ -4872,13 +4872,13 @@
         <v>26432306.47</v>
       </c>
       <c r="S32" t="n">
-        <v>19903484.38</v>
+        <v>19922950.3</v>
       </c>
       <c r="T32" t="n">
-        <v>23688448.79</v>
+        <v>23707914.71</v>
       </c>
       <c r="U32" t="n">
-        <v>20245769.07</v>
+        <v>20245419.15</v>
       </c>
       <c r="V32" t="n">
         <v>3784964.41</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2167358.25</v>
+        <v>2169422.42</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2166113.85</v>
+        <v>2166432.28</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6403,22 +6403,22 @@
         <v>10641.28</v>
       </c>
       <c r="P43" t="n">
-        <v>173078.25</v>
+        <v>176203.45</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>352685.57</v>
+        <v>356585.57</v>
       </c>
       <c r="S43" t="n">
-        <v>123413.37</v>
+        <v>127313.37</v>
       </c>
       <c r="T43" t="n">
-        <v>127349.37</v>
+        <v>131249.37</v>
       </c>
       <c r="U43" t="n">
-        <v>179607.32</v>
+        <v>180382.12</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6552,10 +6552,10 @@
         <v>267451.9</v>
       </c>
       <c r="S44" t="n">
-        <v>72380.13</v>
+        <v>74380.13</v>
       </c>
       <c r="T44" t="n">
-        <v>72380.13</v>
+        <v>74380.13</v>
       </c>
       <c r="U44" t="n">
         <v>150000</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3427759.11</v>
+        <v>3457759.1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3144383.42</v>
+        <v>3157303.15</v>
       </c>
       <c r="P46" t="n">
         <v>21943357.71</v>
@@ -6832,10 +6832,10 @@
         <v>31631816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>6005553.51</v>
+        <v>6007553.51</v>
       </c>
       <c r="T46" t="n">
-        <v>6506003.07</v>
+        <v>6508003.07</v>
       </c>
       <c r="U46" t="n">
         <v>9688458.939999999</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>16039.96</v>
+        <v>28346.18</v>
       </c>
       <c r="S49" t="n">
-        <v>7939.96</v>
+        <v>20246.18</v>
       </c>
       <c r="T49" t="n">
-        <v>7939.96</v>
+        <v>20246.18</v>
       </c>
       <c r="U49" t="n">
-        <v>7939.96</v>
+        <v>20246.18</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>8643538.5</v>
+        <v>9154192.5</v>
       </c>
       <c r="P59" t="n">
         <v>7511479.83</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
         <v>107000</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>657979.71</v>
+        <v>1221962.32</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>99996</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>16574.21</v>
+        <v>28974.21</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18312,10 +18312,10 @@
         <v>36599.31</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>4067.96</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>4067.96</v>
       </c>
       <c r="U128" t="n">
         <v>34599.31</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -23912,10 +23912,10 @@
         <v>1049519.14</v>
       </c>
       <c r="S168" t="n">
-        <v>212219.88</v>
+        <v>215469.88</v>
       </c>
       <c r="T168" t="n">
-        <v>212219.88</v>
+        <v>215469.88</v>
       </c>
       <c r="U168" t="n">
         <v>242859.88</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2025437.07</v>
+        <v>2047783.04</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24189,16 +24189,16 @@
         <v>324976</v>
       </c>
       <c r="R170" t="n">
-        <v>6730981.41</v>
+        <v>6730981.43</v>
       </c>
       <c r="S170" t="n">
-        <v>3028966.42</v>
+        <v>3028966.44</v>
       </c>
       <c r="T170" t="n">
-        <v>3172609.3</v>
+        <v>3172609.32</v>
       </c>
       <c r="U170" t="n">
-        <v>3220428.8</v>
+        <v>3220428.82</v>
       </c>
       <c r="V170" t="n">
         <v>143642.88</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27552,10 +27552,10 @@
         <v>10781639.67</v>
       </c>
       <c r="S194" t="n">
-        <v>7935600</v>
+        <v>9640800</v>
       </c>
       <c r="T194" t="n">
-        <v>8889200</v>
+        <v>10594400</v>
       </c>
       <c r="U194" t="n">
         <v>9641600</v>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28520,7 +28520,7 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>15742.8</v>
+        <v>17710.65</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30763,13 +30763,13 @@
         <v>0</v>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -30778,7 +30778,7 @@
         <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="V217" t="n">
         <v>0</v>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>146651466.23</v>
+        <v>146659768.39</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31892,10 +31892,10 @@
         <v>224565914.38</v>
       </c>
       <c r="S225" t="n">
-        <v>165211987.28</v>
+        <v>166088914.68</v>
       </c>
       <c r="T225" t="n">
-        <v>171550415.91</v>
+        <v>172427343.31</v>
       </c>
       <c r="U225" t="n">
         <v>173542797.58</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52109942.64</v>
+        <v>52252206.54</v>
       </c>
       <c r="S236" t="n">
         <v>41651440.49</v>
@@ -33438,7 +33438,7 @@
         <v>43264204.65</v>
       </c>
       <c r="U236" t="n">
-        <v>43394909.81</v>
+        <v>43537173.71</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>12/10/2026 16:02:37</t>
+          <t>15/10/2026 11:18:53</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>184675.41</v>
+        <v>187325.41</v>
       </c>
       <c r="P7" t="n">
         <v>510399.27</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>165966</v>
       </c>
       <c r="O8" t="n">
-        <v>142145.4</v>
+        <v>142345.15</v>
       </c>
       <c r="P8" t="n">
         <v>287106.31</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5754802.47</v>
+        <v>5767892.47</v>
       </c>
       <c r="P10" t="n">
         <v>9813569.16</v>
@@ -1792,10 +1792,10 @@
         <v>22490631.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11333314.03</v>
+        <v>11861314.03</v>
       </c>
       <c r="T10" t="n">
-        <v>12939717.7</v>
+        <v>13467717.7</v>
       </c>
       <c r="U10" t="n">
         <v>12677062.09</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3743,13 +3743,13 @@
         <v>1440</v>
       </c>
       <c r="P24" t="n">
-        <v>90383.08</v>
+        <v>102436.03</v>
       </c>
       <c r="Q24" t="n">
         <v>169694</v>
       </c>
       <c r="R24" t="n">
-        <v>153262.7</v>
+        <v>182742.03</v>
       </c>
       <c r="S24" t="n">
         <v>40960.6</v>
@@ -3758,7 +3758,7 @@
         <v>40960.6</v>
       </c>
       <c r="U24" t="n">
-        <v>62879.62</v>
+        <v>80306</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12692147.91</v>
+        <v>12952155.84</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>112525.09</v>
+        <v>126412.61</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
         <v>267451.9</v>
       </c>
       <c r="S44" t="n">
-        <v>74380.13</v>
+        <v>70800</v>
       </c>
       <c r="T44" t="n">
         <v>74380.13</v>
@@ -6561,7 +6561,7 @@
         <v>150000</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>3580.13</v>
       </c>
       <c r="W44" t="n">
         <v>150000</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6832,7 @@
         <v>31631816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>6007553.51</v>
+        <v>5993232.97</v>
       </c>
       <c r="T46" t="n">
         <v>6508003.07</v>
@@ -6841,7 +6841,7 @@
         <v>9688458.939999999</v>
       </c>
       <c r="V46" t="n">
-        <v>500449.56</v>
+        <v>514770.1</v>
       </c>
       <c r="W46" t="n">
         <v>10125997.24</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>28346.18</v>
+        <v>40279.96</v>
       </c>
       <c r="S49" t="n">
-        <v>20246.18</v>
+        <v>32179.96</v>
       </c>
       <c r="T49" t="n">
-        <v>20246.18</v>
+        <v>32179.96</v>
       </c>
       <c r="U49" t="n">
-        <v>20246.18</v>
+        <v>32179.96</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11163,13 +11163,13 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>299999.98</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -11178,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>149999.98</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -14118,7 +14118,7 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>7661.58</v>
+        <v>7811.58</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="S124" t="n">
         <v>200000</v>
@@ -17758,7 +17758,7 @@
         <v>200000</v>
       </c>
       <c r="U124" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>8044178.59</v>
+        <v>8802384.41</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>30678.28</v>
+        <v>31053.28</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1763164.64</v>
+        <v>1783290.42</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>145445519.3</v>
+        <v>145504152.89</v>
       </c>
       <c r="P225" t="n">
         <v>51023116.8</v>
@@ -31892,10 +31892,10 @@
         <v>224565914.38</v>
       </c>
       <c r="S225" t="n">
-        <v>166088914.68</v>
+        <v>166527378.38</v>
       </c>
       <c r="T225" t="n">
-        <v>172427343.31</v>
+        <v>172865807.01</v>
       </c>
       <c r="U225" t="n">
         <v>173542797.58</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32300,7 +32300,7 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>81734533.70999999</v>
+        <v>83680665.70999999</v>
       </c>
       <c r="P228" t="n">
         <v>88356395.75</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>62618122.08</v>
+        <v>62708122.08</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>62245695.96</v>
+        <v>62459940.24</v>
       </c>
       <c r="P229" t="n">
         <v>51388595.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>39113895.79</v>
+        <v>39377962.79</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>15/10/2026 11:18:53</t>
+          <t>16/10/2026 11:02:43</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>48647</v>
       </c>
       <c r="R6" t="n">
-        <v>282106.01</v>
+        <v>286378.01</v>
       </c>
       <c r="S6" t="n">
         <v>134445.61</v>
@@ -1238,7 +1238,7 @@
         <v>183363.95</v>
       </c>
       <c r="U6" t="n">
-        <v>203117.81</v>
+        <v>207389.81</v>
       </c>
       <c r="V6" t="n">
         <v>48918.34</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>187325.41</v>
+        <v>222325.41</v>
       </c>
       <c r="P7" t="n">
         <v>510399.27</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>165966</v>
       </c>
       <c r="O8" t="n">
-        <v>142345.15</v>
+        <v>144952.35</v>
       </c>
       <c r="P8" t="n">
         <v>287106.31</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>224084.87</v>
+        <v>231820.55</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="O18" t="n">
-        <v>1185724.86</v>
+        <v>1335699.33</v>
       </c>
       <c r="P18" t="n">
         <v>26813.15</v>
@@ -2924,7 +2924,7 @@
         <v>19112.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1800000</v>
+        <v>1880000</v>
       </c>
       <c r="X18" t="n">
         <v>1800000</v>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1800000</v>
+        <v>1880000</v>
       </c>
       <c r="AB18" t="n">
         <v>5</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>22000000</v>
+        <v>21550000</v>
       </c>
       <c r="X26" t="n">
         <v>22000000</v>
@@ -4053,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AA26" t="n">
-        <v>22000000</v>
+        <v>21550000</v>
       </c>
       <c r="AB26" t="n">
         <v>5</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O27" t="n">
         <v>30832.63</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X27" t="n">
         <v>50000</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AB27" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1308912.66</v>
+        <v>1309488.61</v>
       </c>
       <c r="P30" t="n">
         <v>714645.38</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>11564529.15</v>
+        <v>11795178.1</v>
       </c>
       <c r="P32" t="n">
         <v>6186887.32</v>
@@ -4869,7 +4869,7 @@
         <v>103049</v>
       </c>
       <c r="R32" t="n">
-        <v>26432306.47</v>
+        <v>26432467.54</v>
       </c>
       <c r="S32" t="n">
         <v>19922950.3</v>
@@ -4878,7 +4878,7 @@
         <v>23707914.71</v>
       </c>
       <c r="U32" t="n">
-        <v>20245419.15</v>
+        <v>20245580.22</v>
       </c>
       <c r="V32" t="n">
         <v>3784964.41</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="O35" t="n">
         <v>3360002.96</v>
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4418000</v>
+        <v>4818000</v>
       </c>
       <c r="X35" t="n">
         <v>4418000</v>
@@ -5316,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4418000</v>
+        <v>4818000</v>
       </c>
       <c r="AB35" t="n">
         <v>5</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2166432.28</v>
+        <v>2168496.45</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3457759.1</v>
+        <v>3462371.69</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6823,22 +6823,22 @@
         <v>3157303.15</v>
       </c>
       <c r="P46" t="n">
-        <v>21943357.71</v>
+        <v>22073303.01</v>
       </c>
       <c r="Q46" t="n">
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31631816.65</v>
+        <v>31791816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>5993232.97</v>
+        <v>5997001.22</v>
       </c>
       <c r="T46" t="n">
-        <v>6508003.07</v>
+        <v>6511771.32</v>
       </c>
       <c r="U46" t="n">
-        <v>9688458.939999999</v>
+        <v>9718513.640000001</v>
       </c>
       <c r="V46" t="n">
         <v>514770.1</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>7612695.77</v>
+        <v>8777361.949999999</v>
       </c>
       <c r="P52" t="n">
         <v>5913951.99</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>439634</v>
+        <v>534355.52</v>
       </c>
       <c r="S82" t="n">
         <v>439634</v>
@@ -11878,7 +11878,7 @@
         <v>439634</v>
       </c>
       <c r="U82" t="n">
-        <v>439634</v>
+        <v>534355.52</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
         <v>8049</v>
       </c>
       <c r="O88" t="n">
-        <v>1191556.45</v>
+        <v>1199605.4</v>
       </c>
       <c r="P88" t="n">
         <v>0.05</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1126850</v>
+        <v>1261700</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16769,16 +16769,16 @@
         <v>57248</v>
       </c>
       <c r="R117" t="n">
-        <v>446377.55</v>
+        <v>476377.55</v>
       </c>
       <c r="S117" t="n">
-        <v>363452.83</v>
+        <v>393452.83</v>
       </c>
       <c r="T117" t="n">
-        <v>363452.83</v>
+        <v>393452.83</v>
       </c>
       <c r="U117" t="n">
-        <v>392635.02</v>
+        <v>422635.02</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>185000</v>
+        <v>385000</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -20278,7 +20278,7 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>185000</v>
+        <v>385000</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
         <v>11000</v>
       </c>
       <c r="W158" t="n">
-        <v>7239296</v>
+        <v>7159296</v>
       </c>
       <c r="X158" t="n">
         <v>8429440</v>
@@ -22533,10 +22533,10 @@
         <v>65000</v>
       </c>
       <c r="Z158" t="n">
-        <v>1190144</v>
+        <v>1270144</v>
       </c>
       <c r="AA158" t="n">
-        <v>7239296</v>
+        <v>7159296</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <v>259262</v>
       </c>
       <c r="O168" t="n">
-        <v>136238.21</v>
+        <v>136894.21</v>
       </c>
       <c r="P168" t="n">
         <v>806659.26</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27680,7 @@
         <v>8495211.470000001</v>
       </c>
       <c r="O195" t="n">
-        <v>24837570.18</v>
+        <v>27454785.08</v>
       </c>
       <c r="P195" t="n">
         <v>5599952.69</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -27820,7 +27820,7 @@
         <v>52998</v>
       </c>
       <c r="O196" t="n">
-        <v>90884.2</v>
+        <v>91465.2</v>
       </c>
       <c r="P196" t="n">
         <v>67022.03</v>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1783290.42</v>
+        <v>1785314.58</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28243,7 +28243,7 @@
         <v>1736975.36</v>
       </c>
       <c r="P199" t="n">
-        <v>2763223.97</v>
+        <v>2763454.97</v>
       </c>
       <c r="Q199" t="n">
         <v>65487</v>
@@ -28252,13 +28252,13 @@
         <v>6089210.8</v>
       </c>
       <c r="S199" t="n">
-        <v>2482175.87</v>
+        <v>2532388.5</v>
       </c>
       <c r="T199" t="n">
-        <v>2586523.63</v>
+        <v>2636736.26</v>
       </c>
       <c r="U199" t="n">
-        <v>3325986.83</v>
+        <v>3325755.83</v>
       </c>
       <c r="V199" t="n">
         <v>104347.76</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>356543.33</v>
+        <v>360338.1</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29783,7 +29783,7 @@
         <v>356543.33</v>
       </c>
       <c r="P210" t="n">
-        <v>4909802.89</v>
+        <v>4910264.89</v>
       </c>
       <c r="Q210" t="n">
         <v>5886824</v>
@@ -29792,13 +29792,13 @@
         <v>7831398.86</v>
       </c>
       <c r="S210" t="n">
-        <v>559609.14</v>
+        <v>569682.72</v>
       </c>
       <c r="T210" t="n">
-        <v>2453838.77</v>
+        <v>2463912.35</v>
       </c>
       <c r="U210" t="n">
-        <v>2921595.97</v>
+        <v>2921133.97</v>
       </c>
       <c r="V210" t="n">
         <v>1894229.63</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>31800</v>
+        <v>33200</v>
       </c>
       <c r="P213" t="n">
         <v>11400</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>145504152.89</v>
+        <v>146651466.23</v>
       </c>
       <c r="P225" t="n">
         <v>51023116.8</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>62708122.08</v>
+        <v>64662559.74</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>38438022.79</v>
+        <v>38845761.79</v>
       </c>
       <c r="P236" t="n">
         <v>8715032.83</v>
@@ -33429,7 +33429,7 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52252206.54</v>
+        <v>52450231.14</v>
       </c>
       <c r="S236" t="n">
         <v>41651440.49</v>
@@ -33438,7 +33438,7 @@
         <v>43264204.65</v>
       </c>
       <c r="U236" t="n">
-        <v>43537173.71</v>
+        <v>43735198.31</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>16/10/2026 11:02:43</t>
+          <t>17/10/2026 10:07:57</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>17/10/2026 10:07:57</t>
+          <t>18/10/2026 10:16:27</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>18/10/2026 10:16:27</t>
+          <t>19/10/2026 13:37:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1792,10 +1792,10 @@
         <v>22490631.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11861314.03</v>
+        <v>11978323.68</v>
       </c>
       <c r="T10" t="n">
-        <v>13467717.7</v>
+        <v>13584727.35</v>
       </c>
       <c r="U10" t="n">
         <v>12677062.09</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2772,10 @@
         <v>301525.7</v>
       </c>
       <c r="S17" t="n">
-        <v>71840.72</v>
+        <v>75640.72</v>
       </c>
       <c r="T17" t="n">
-        <v>71840.72</v>
+        <v>75640.72</v>
       </c>
       <c r="U17" t="n">
         <v>285000</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -4872,10 +4872,10 @@
         <v>26432467.54</v>
       </c>
       <c r="S32" t="n">
-        <v>19922950.3</v>
+        <v>19923111.37</v>
       </c>
       <c r="T32" t="n">
-        <v>23707914.71</v>
+        <v>23708075.78</v>
       </c>
       <c r="U32" t="n">
         <v>20245580.22</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2169422.42</v>
+        <v>2421823.38</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
         <v>3157303.15</v>
       </c>
       <c r="P46" t="n">
-        <v>22073303.01</v>
+        <v>25026550</v>
       </c>
       <c r="Q46" t="n">
         <v>5379029</v>
@@ -6838,7 +6838,7 @@
         <v>6511771.32</v>
       </c>
       <c r="U46" t="n">
-        <v>9718513.640000001</v>
+        <v>6765266.65</v>
       </c>
       <c r="V46" t="n">
         <v>514770.1</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="S85" t="n">
         <v>150000</v>
@@ -12298,7 +12298,7 @@
         <v>150000</v>
       </c>
       <c r="U85" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16772,10 +16772,10 @@
         <v>476377.55</v>
       </c>
       <c r="S117" t="n">
-        <v>393452.83</v>
+        <v>408381.59</v>
       </c>
       <c r="T117" t="n">
-        <v>393452.83</v>
+        <v>408381.59</v>
       </c>
       <c r="U117" t="n">
         <v>422635.02</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18312,10 +18312,10 @@
         <v>36599.31</v>
       </c>
       <c r="S128" t="n">
-        <v>4067.96</v>
+        <v>26007.76</v>
       </c>
       <c r="T128" t="n">
-        <v>4067.96</v>
+        <v>26007.76</v>
       </c>
       <c r="U128" t="n">
         <v>34599.31</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22643,13 +22643,13 @@
         <v>5442598.8</v>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>406807.6</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>6744400.76</v>
+        <v>7151208.36</v>
       </c>
       <c r="S159" t="n">
         <v>5442598.8</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32303,7 +32303,7 @@
         <v>83680665.70999999</v>
       </c>
       <c r="P228" t="n">
-        <v>88356395.75</v>
+        <v>96812362.8</v>
       </c>
       <c r="Q228" t="n">
         <v>4727853</v>
@@ -32312,16 +32312,16 @@
         <v>217416742</v>
       </c>
       <c r="S228" t="n">
-        <v>121904379.2</v>
+        <v>120604379.2</v>
       </c>
       <c r="T228" t="n">
         <v>121904379.2</v>
       </c>
       <c r="U228" t="n">
-        <v>129060346.25</v>
+        <v>120604379.2</v>
       </c>
       <c r="V228" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="W228" t="n">
         <v>129060346.25</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>
@@ -33423,13 +33423,13 @@
         <v>38845761.79</v>
       </c>
       <c r="P236" t="n">
-        <v>8715032.83</v>
+        <v>8781112.83</v>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52450231.14</v>
+        <v>52659144.46</v>
       </c>
       <c r="S236" t="n">
         <v>41651440.49</v>
@@ -33438,7 +33438,7 @@
         <v>43264204.65</v>
       </c>
       <c r="U236" t="n">
-        <v>43735198.31</v>
+        <v>43878031.63</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>19/10/2026 13:37:23</t>
+          <t>20/10/2026 11:22:10</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>134445.61</v>
+        <v>138717.61</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>286378.01</v>
       </c>
       <c r="S6" t="n">
-        <v>134445.61</v>
+        <v>138717.61</v>
       </c>
       <c r="T6" t="n">
-        <v>183363.95</v>
+        <v>187635.95</v>
       </c>
       <c r="U6" t="n">
         <v>207389.81</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>200936.59</v>
+        <v>253723.2</v>
       </c>
       <c r="P9" t="n">
         <v>558517.84</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6326046.26</v>
+        <v>7607433.05</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5767892.47</v>
+        <v>6089757.42</v>
       </c>
       <c r="P10" t="n">
         <v>9813569.16</v>
@@ -1804,7 +1804,7 @@
         <v>1606403.67</v>
       </c>
       <c r="W10" t="n">
-        <v>12746699.12</v>
+        <v>12744680</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1813,10 +1813,10 @@
         <v>3127008</v>
       </c>
       <c r="Z10" t="n">
-        <v>3918399.85</v>
+        <v>3920418.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>12746699.12</v>
+        <v>12744680</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>231820.55</v>
+        <v>231895.55</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2772,10 @@
         <v>301525.7</v>
       </c>
       <c r="S17" t="n">
-        <v>75640.72</v>
+        <v>77225.72</v>
       </c>
       <c r="T17" t="n">
-        <v>75640.72</v>
+        <v>77225.72</v>
       </c>
       <c r="U17" t="n">
         <v>285000</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="O21" t="n">
         <v>1631.04</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="S21" t="n">
         <v>1631.04</v>
@@ -3338,13 +3338,13 @@
         <v>1631.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="AB21" t="n">
         <v>5</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1460678.1</v>
+        <v>1466847.08</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1309488.61</v>
+        <v>1456720.57</v>
       </c>
       <c r="P30" t="n">
         <v>714645.38</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3151167.44</v>
+        <v>3882992.85</v>
       </c>
       <c r="P31" t="n">
         <v>9202815.26</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12952155.84</v>
+        <v>12960544.58</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>11795178.1</v>
+        <v>11850040.03</v>
       </c>
       <c r="P32" t="n">
         <v>6186887.32</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>527764.12</v>
+        <v>558902.5600000001</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2168496.45</v>
+        <v>2169422.42</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3157303.15</v>
+        <v>3247467.62</v>
       </c>
       <c r="P46" t="n">
         <v>25026550</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7939.96</v>
+        <v>13906.85</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
         <v>217009.89</v>
       </c>
       <c r="O53" t="n">
-        <v>155252.3</v>
+        <v>188253.47</v>
       </c>
       <c r="P53" t="n">
         <v>201637.53</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1261700</v>
+        <v>1260150</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1261700</v>
+        <v>1260150</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -13698,7 +13698,7 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>8342.23</v>
+        <v>8492.23</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>7811.58</v>
+        <v>7959.12</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1690301.29</v>
+        <v>1694326.09</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>72910.97</v>
       </c>
       <c r="O116" t="n">
-        <v>45683.89</v>
+        <v>76195</v>
       </c>
       <c r="P116" t="n">
         <v>223741.58</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>212807.32</v>
+        <v>240833.5</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>9169573.33</v>
+        <v>8445809.92</v>
       </c>
       <c r="X143" t="n">
         <v>12675633</v>
@@ -20433,10 +20433,10 @@
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>3506059.67</v>
+        <v>4229823.08</v>
       </c>
       <c r="AA143" t="n">
-        <v>9169573.33</v>
+        <v>8445809.92</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22643,13 +22643,13 @@
         <v>5442598.8</v>
       </c>
       <c r="P159" t="n">
-        <v>406807.6</v>
+        <v>1136263.01</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>7151208.36</v>
+        <v>7880663.77</v>
       </c>
       <c r="S159" t="n">
         <v>5442598.8</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
         <v>234940.86</v>
       </c>
       <c r="O162" t="n">
-        <v>200936.19</v>
+        <v>249508.12</v>
       </c>
       <c r="P162" t="n">
         <v>309378.12</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>271122.52</v>
+        <v>272222.1</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23331,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>31523.58</v>
+        <v>31879.22</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>31053.28</v>
+        <v>31495.9</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1923344.33</v>
+        <v>1974390.7</v>
       </c>
       <c r="P170" t="n">
         <v>3510552.61</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>181507.55</v>
+        <v>184005.97</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27680,7 @@
         <v>8495211.470000001</v>
       </c>
       <c r="O195" t="n">
-        <v>27454785.08</v>
+        <v>29390686.85</v>
       </c>
       <c r="P195" t="n">
         <v>5599952.69</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>97412.85000000001</v>
+        <v>108839.25</v>
       </c>
       <c r="P197" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>908634.71</v>
+        <v>1167627.94</v>
       </c>
       <c r="P198" t="n">
         <v>2614040.51</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1785314.58</v>
+        <v>1785434.38</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>360338.1</v>
+        <v>360517.8</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>33200</v>
+        <v>35300</v>
       </c>
       <c r="P213" t="n">
         <v>11400</v>
@@ -30212,7 +30212,7 @@
         <v>50100</v>
       </c>
       <c r="S213" t="n">
-        <v>38100</v>
+        <v>37400</v>
       </c>
       <c r="T213" t="n">
         <v>38700</v>
@@ -30221,7 +30221,7 @@
         <v>38700</v>
       </c>
       <c r="V213" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="W213" t="n">
         <v>46881</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>146659768.39</v>
+        <v>146839956.6</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31892,10 +31892,10 @@
         <v>224565914.38</v>
       </c>
       <c r="S225" t="n">
-        <v>166527378.38</v>
+        <v>166965842.08</v>
       </c>
       <c r="T225" t="n">
-        <v>172865807.01</v>
+        <v>173304270.71</v>
       </c>
       <c r="U225" t="n">
         <v>173542797.58</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>64662559.74</v>
+        <v>66462559.74</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32720,7 +32720,7 @@
         <v>1406720</v>
       </c>
       <c r="O231" t="n">
-        <v>907561.39</v>
+        <v>1023951.79</v>
       </c>
       <c r="P231" t="n">
         <v>0</v>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>38845761.79</v>
+        <v>39113895.79</v>
       </c>
       <c r="P236" t="n">
         <v>8781112.83</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>20/10/2026 11:22:10</t>
+          <t>21/10/2026 11:41:02</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7607433.05</v>
+        <v>7609299.65</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6089757.42</v>
+        <v>6092130.32</v>
       </c>
       <c r="P10" t="n">
         <v>9813569.16</v>
@@ -1792,10 +1792,10 @@
         <v>22490631.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11978323.68</v>
+        <v>11978872.85</v>
       </c>
       <c r="T10" t="n">
-        <v>13584727.35</v>
+        <v>13585276.52</v>
       </c>
       <c r="U10" t="n">
         <v>12677062.09</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1466847.08</v>
+        <v>1467726.86</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1456720.57</v>
+        <v>1460678.1</v>
       </c>
       <c r="P30" t="n">
         <v>714645.38</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>558902.5600000001</v>
+        <v>559194.2</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>600000</v>
       </c>
       <c r="O36" t="n">
-        <v>2169422.42</v>
+        <v>2417307.61</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3462371.69</v>
+        <v>3478770.59</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3247467.62</v>
+        <v>3277467.62</v>
       </c>
       <c r="P46" t="n">
         <v>25026550</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17612,10 +17612,10 @@
         <v>450000</v>
       </c>
       <c r="S123" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="T123" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="U123" t="n">
         <v>450000</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22512,10 +22512,10 @@
         <v>23928833.61</v>
       </c>
       <c r="S158" t="n">
-        <v>2745814.21</v>
+        <v>2768039.4</v>
       </c>
       <c r="T158" t="n">
-        <v>2756814.21</v>
+        <v>2779039.4</v>
       </c>
       <c r="U158" t="n">
         <v>7148138.71</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23331,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>31879.22</v>
+        <v>32025.97</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>152184.37</v>
+        <v>152520.16</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -23900,7 +23900,7 @@
         <v>259262</v>
       </c>
       <c r="O168" t="n">
-        <v>136894.21</v>
+        <v>151640.37</v>
       </c>
       <c r="P168" t="n">
         <v>806659.26</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2047783.04</v>
+        <v>2058640.4</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26557,7 +26557,7 @@
         <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>578000</v>
+        <v>728000</v>
       </c>
       <c r="O187" t="n">
         <v>578000</v>
@@ -26584,7 +26584,7 @@
         <v>0</v>
       </c>
       <c r="W187" t="n">
-        <v>578000</v>
+        <v>728000</v>
       </c>
       <c r="X187" t="n">
         <v>0</v>
@@ -26596,7 +26596,7 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>578000</v>
+        <v>728000</v>
       </c>
       <c r="AB187" t="n">
         <v>5</v>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1785434.38</v>
+        <v>1813221.83</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>360517.8</v>
+        <v>398576.01</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29783,22 +29783,22 @@
         <v>356543.33</v>
       </c>
       <c r="P210" t="n">
-        <v>4910264.89</v>
+        <v>4930699.09</v>
       </c>
       <c r="Q210" t="n">
         <v>5886824</v>
       </c>
       <c r="R210" t="n">
-        <v>7831398.86</v>
+        <v>7852295.06</v>
       </c>
       <c r="S210" t="n">
-        <v>569682.72</v>
+        <v>590427.91</v>
       </c>
       <c r="T210" t="n">
-        <v>2463912.35</v>
+        <v>2484657.54</v>
       </c>
       <c r="U210" t="n">
-        <v>2921133.97</v>
+        <v>2921595.97</v>
       </c>
       <c r="V210" t="n">
         <v>1894229.63</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>146651466.23</v>
+        <v>146659768.39</v>
       </c>
       <c r="P225" t="n">
         <v>51023116.8</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32300,7 +32300,7 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>83680665.70999999</v>
+        <v>86108915.70999999</v>
       </c>
       <c r="P228" t="n">
         <v>96812362.8</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>66462559.74</v>
+        <v>67364819.45999999</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,16 +32440,16 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>62459940.24</v>
+        <v>62618122.08</v>
       </c>
       <c r="P229" t="n">
-        <v>51388595.59</v>
+        <v>51538399.59</v>
       </c>
       <c r="Q229" t="n">
         <v>2792377</v>
       </c>
       <c r="R229" t="n">
-        <v>130831621.59</v>
+        <v>130981425.59</v>
       </c>
       <c r="S229" t="n">
         <v>78778260.98999999</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>
@@ -33423,7 +33423,7 @@
         <v>39113895.79</v>
       </c>
       <c r="P236" t="n">
-        <v>8781112.83</v>
+        <v>8829908.050000001</v>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
@@ -33432,13 +33432,13 @@
         <v>52659144.46</v>
       </c>
       <c r="S236" t="n">
-        <v>41651440.49</v>
+        <v>41891730.93</v>
       </c>
       <c r="T236" t="n">
-        <v>43264204.65</v>
+        <v>43504495.09</v>
       </c>
       <c r="U236" t="n">
-        <v>43878031.63</v>
+        <v>43829236.41</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>21/10/2026 11:41:02</t>
+          <t>22/10/2026 11:35:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>222325.41</v>
+        <v>257827.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7609299.65</v>
+        <v>7618475.13</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6092130.32</v>
+        <v>6094698.48</v>
       </c>
       <c r="P10" t="n">
         <v>9813569.16</v>
@@ -1792,10 +1792,10 @@
         <v>22490631.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11978872.85</v>
+        <v>11981675.11</v>
       </c>
       <c r="T10" t="n">
-        <v>13585276.52</v>
+        <v>13588078.78</v>
       </c>
       <c r="U10" t="n">
         <v>12677062.09</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4068546.28</v>
+        <v>4603998.9</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1467726.86</v>
+        <v>1467855.72</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12960544.58</v>
+        <v>12961126.95</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>561146.24</v>
+        <v>583173.17</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>11797.68</v>
+        <v>15997.68</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3478770.59</v>
+        <v>3480839.09</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>13906.85</v>
+        <v>20059.96</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11592,10 +11592,10 @@
         <v>500000</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="U80" t="n">
         <v>500000</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
         <v>237000</v>
       </c>
       <c r="O90" t="n">
-        <v>657979.71</v>
+        <v>1221962.32</v>
       </c>
       <c r="P90" t="n">
         <v>956845.74</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -14118,7 +14118,7 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>130683.3</v>
+        <v>130752.4</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17329,7 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -17338,7 +17338,7 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>272222.1</v>
+        <v>272291.2</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2058640.4</v>
+        <v>2078879.83</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1974390.7</v>
+        <v>1988736.67</v>
       </c>
       <c r="P170" t="n">
         <v>3510552.61</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>85383.75999999999</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -25178,7 +25178,7 @@
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>0</v>
+        <v>85383.75999999999</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>29390686.85</v>
+        <v>29737656.95</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28252,10 +28252,10 @@
         <v>6089210.8</v>
       </c>
       <c r="S199" t="n">
-        <v>2532388.5</v>
+        <v>2978841.74</v>
       </c>
       <c r="T199" t="n">
-        <v>2636736.26</v>
+        <v>3083189.5</v>
       </c>
       <c r="U199" t="n">
         <v>3325755.83</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>398576.01</v>
+        <v>398610.56</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>146839956.6</v>
+        <v>147497652.15</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>67364819.45999999</v>
+        <v>68354819.45999999</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52659144.46</v>
+        <v>52821037.12</v>
       </c>
       <c r="S236" t="n">
         <v>41891730.93</v>
@@ -33438,7 +33438,7 @@
         <v>43504495.09</v>
       </c>
       <c r="U236" t="n">
-        <v>43829236.41</v>
+        <v>43991129.07</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>22/10/2026 11:35:39</t>
+          <t>23/10/2026 11:22:59</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>165966</v>
       </c>
       <c r="O8" t="n">
-        <v>144952.35</v>
+        <v>156807.77</v>
       </c>
       <c r="P8" t="n">
         <v>287106.31</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7618475.13</v>
+        <v>7637104.25</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,22 +1783,22 @@
         <v>6094698.48</v>
       </c>
       <c r="P10" t="n">
-        <v>9813569.16</v>
+        <v>9822561.83</v>
       </c>
       <c r="Q10" t="n">
         <v>3127008</v>
       </c>
       <c r="R10" t="n">
-        <v>22490631.25</v>
+        <v>22519187.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11981675.11</v>
+        <v>11991393.37</v>
       </c>
       <c r="T10" t="n">
-        <v>13588078.78</v>
+        <v>13597797.04</v>
       </c>
       <c r="U10" t="n">
-        <v>12677062.09</v>
+        <v>12696625.42</v>
       </c>
       <c r="V10" t="n">
         <v>1606403.67</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>182179.94</v>
+        <v>186539.94</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12961126.95</v>
+        <v>12990006.08</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>11850040.03</v>
+        <v>12110047.96</v>
       </c>
       <c r="P32" t="n">
         <v>6186887.32</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>583173.17</v>
+        <v>584278.01</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>10641.28</v>
+        <v>11797.68</v>
       </c>
       <c r="P43" t="n">
         <v>176203.45</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>46100</v>
       </c>
       <c r="O49" t="n">
-        <v>7939.96</v>
+        <v>13906.85</v>
       </c>
       <c r="P49" t="n">
         <v>8100</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -16918,7 +16918,7 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20272,10 +20272,10 @@
         <v>385000</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="U142" t="n">
         <v>385000</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>8044178.59</v>
+        <v>8802384.41</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22652,10 +22652,10 @@
         <v>7880663.77</v>
       </c>
       <c r="S159" t="n">
-        <v>5442598.8</v>
+        <v>5765246.61</v>
       </c>
       <c r="T159" t="n">
-        <v>9027497.199999999</v>
+        <v>9350145.01</v>
       </c>
       <c r="U159" t="n">
         <v>6744400.76</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28240,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1736975.36</v>
+        <v>1757101.14</v>
       </c>
       <c r="P199" t="n">
-        <v>2763454.97</v>
+        <v>2765860.31</v>
       </c>
       <c r="Q199" t="n">
         <v>65487</v>
@@ -28252,13 +28252,13 @@
         <v>6089210.8</v>
       </c>
       <c r="S199" t="n">
-        <v>2978841.74</v>
+        <v>3018930.74</v>
       </c>
       <c r="T199" t="n">
-        <v>3083189.5</v>
+        <v>3123278.5</v>
       </c>
       <c r="U199" t="n">
-        <v>3325755.83</v>
+        <v>3323350.49</v>
       </c>
       <c r="V199" t="n">
         <v>104347.76</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29792,10 +29792,10 @@
         <v>7852295.06</v>
       </c>
       <c r="S210" t="n">
-        <v>590427.91</v>
+        <v>598347.95</v>
       </c>
       <c r="T210" t="n">
-        <v>2484657.54</v>
+        <v>2492577.58</v>
       </c>
       <c r="U210" t="n">
         <v>2921595.97</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>296.92</v>
+        <v>326.92</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30352,10 +30352,10 @@
         <v>95090.62</v>
       </c>
       <c r="S214" t="n">
-        <v>42280.65</v>
+        <v>61421.62</v>
       </c>
       <c r="T214" t="n">
-        <v>42280.65</v>
+        <v>61421.62</v>
       </c>
       <c r="U214" t="n">
         <v>75949.64999999999</v>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>62618122.08</v>
+        <v>62708122.08</v>
       </c>
       <c r="P229" t="n">
         <v>51538399.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>39113895.79</v>
+        <v>39377962.79</v>
       </c>
       <c r="P236" t="n">
         <v>8829908.050000001</v>
@@ -33429,7 +33429,7 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52821037.12</v>
+        <v>52886531.98</v>
       </c>
       <c r="S236" t="n">
         <v>41891730.93</v>
@@ -33438,7 +33438,7 @@
         <v>43504495.09</v>
       </c>
       <c r="U236" t="n">
-        <v>43991129.07</v>
+        <v>44056623.93</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>23/10/2026 11:22:59</t>
+          <t>24/10/2026 10:22:54</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>24/10/2026 10:22:54</t>
+          <t>25/10/2026 10:54:56</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>25/10/2026 10:54:56</t>
+          <t>26/10/2026 13:11:18</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>208502.16</v>
+        <v>209321.41</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -3332,10 +3332,10 @@
         <v>727413.5699999999</v>
       </c>
       <c r="S21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1631.04</v>
+        <v>727413.5699999999</v>
       </c>
       <c r="U21" t="n">
         <v>727413.5699999999</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>11823903.46</v>
+        <v>13080651.9</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>11825408.72</v>
+        <v>13082157.16</v>
       </c>
       <c r="S26" t="n">
-        <v>11825408.72</v>
+        <v>13082157.16</v>
       </c>
       <c r="T26" t="n">
-        <v>11825408.72</v>
+        <v>13082157.16</v>
       </c>
       <c r="U26" t="n">
-        <v>11825408.72</v>
+        <v>13082157.16</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3360002.96</v>
+        <v>3728032.23</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3360002.96</v>
+        <v>3728032.23</v>
       </c>
       <c r="S35" t="n">
-        <v>3360002.96</v>
+        <v>3728032.23</v>
       </c>
       <c r="T35" t="n">
-        <v>3360002.96</v>
+        <v>3728032.23</v>
       </c>
       <c r="U35" t="n">
-        <v>3360002.96</v>
+        <v>3728032.23</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>198540.72</v>
+        <v>202752.63</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         <v>50000</v>
       </c>
       <c r="O55" t="n">
-        <v>24792.87</v>
+        <v>24977.41</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>190000</v>
+        <v>296101.6</v>
       </c>
       <c r="S92" t="n">
         <v>190000</v>
@@ -13278,7 +13278,7 @@
         <v>190000</v>
       </c>
       <c r="U92" t="n">
-        <v>190000</v>
+        <v>296101.6</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>99996</v>
+        <v>149996</v>
       </c>
       <c r="S93" t="n">
         <v>99996</v>
@@ -13418,7 +13418,7 @@
         <v>99996</v>
       </c>
       <c r="U93" t="n">
-        <v>99996</v>
+        <v>149996</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27683,13 +27683,13 @@
         <v>29390686.85</v>
       </c>
       <c r="P195" t="n">
-        <v>5599952.69</v>
+        <v>5985218.31</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>36521519.16</v>
+        <v>36906787.78</v>
       </c>
       <c r="S195" t="n">
         <v>30126000.12</v>
@@ -27698,7 +27698,7 @@
         <v>31060316.58</v>
       </c>
       <c r="U195" t="n">
-        <v>30921566.47</v>
+        <v>30921569.47</v>
       </c>
       <c r="V195" t="n">
         <v>934316.46</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28383,7 +28383,7 @@
         <v>368.19</v>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="Q200" t="n">
         <v>0</v>
@@ -28392,16 +28392,16 @@
         <v>80100</v>
       </c>
       <c r="S200" t="n">
-        <v>73100</v>
+        <v>58100</v>
       </c>
       <c r="T200" t="n">
         <v>80100</v>
       </c>
       <c r="U200" t="n">
-        <v>80100</v>
+        <v>58100</v>
       </c>
       <c r="V200" t="n">
-        <v>7000</v>
+        <v>22000</v>
       </c>
       <c r="W200" t="n">
         <v>139282</v>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>147497652.15</v>
+        <v>148027956.39</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>146659768.39</v>
+        <v>146759284.25</v>
       </c>
       <c r="P225" t="n">
         <v>51023116.8</v>
@@ -31892,10 +31892,10 @@
         <v>224565914.38</v>
       </c>
       <c r="S225" t="n">
-        <v>166965842.08</v>
+        <v>168281233.18</v>
       </c>
       <c r="T225" t="n">
-        <v>173304270.71</v>
+        <v>174619661.81</v>
       </c>
       <c r="U225" t="n">
         <v>173542797.58</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>68354819.45999999</v>
+        <v>68804819.45999999</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,7 +32440,7 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>62708122.08</v>
+        <v>64508122.08</v>
       </c>
       <c r="P229" t="n">
         <v>51538399.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>52886531.98</v>
+        <v>52909523.45</v>
       </c>
       <c r="S236" t="n">
         <v>41891730.93</v>
@@ -33438,7 +33438,7 @@
         <v>43504495.09</v>
       </c>
       <c r="U236" t="n">
-        <v>44056623.93</v>
+        <v>44079615.4</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>26/10/2026 13:11:18</t>
+          <t>27/10/2026 12:30:52</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>257827.41</v>
+        <v>274029.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6094698.48</v>
+        <v>6095657.28</v>
       </c>
       <c r="P10" t="n">
         <v>9822561.83</v>
@@ -1792,10 +1792,10 @@
         <v>22519187.25</v>
       </c>
       <c r="S10" t="n">
-        <v>11991393.37</v>
+        <v>12001747.12</v>
       </c>
       <c r="T10" t="n">
-        <v>13597797.04</v>
+        <v>13608150.79</v>
       </c>
       <c r="U10" t="n">
         <v>12696625.42</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1467855.72</v>
+        <v>1468104.34</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1460678.1</v>
+        <v>1466098.14</v>
       </c>
       <c r="P30" t="n">
         <v>714645.38</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3728032.23</v>
+        <v>3727768.19</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3480839.09</v>
+        <v>3481169.09</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,31 +6820,31 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>3277467.62</v>
+        <v>3341151.42</v>
       </c>
       <c r="P46" t="n">
-        <v>25026550</v>
+        <v>25093434.29</v>
       </c>
       <c r="Q46" t="n">
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31791816.65</v>
+        <v>31859030.94</v>
       </c>
       <c r="S46" t="n">
-        <v>5997001.22</v>
+        <v>5997331.22</v>
       </c>
       <c r="T46" t="n">
-        <v>6511771.32</v>
+        <v>6512431.32</v>
       </c>
       <c r="U46" t="n">
-        <v>6765266.65</v>
+        <v>6765596.65</v>
       </c>
       <c r="V46" t="n">
-        <v>514770.1</v>
+        <v>515100.1</v>
       </c>
       <c r="W46" t="n">
-        <v>10125997.24</v>
+        <v>7171925.29</v>
       </c>
       <c r="X46" t="n">
         <v>21072104</v>
@@ -6853,10 +6853,10 @@
         <v>5379029</v>
       </c>
       <c r="Z46" t="n">
-        <v>11039992.76</v>
+        <v>13994064.71</v>
       </c>
       <c r="AA46" t="n">
-        <v>10125997.24</v>
+        <v>7171925.29</v>
       </c>
       <c r="AB46" t="n">
         <v>5</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="S102" t="n">
         <v>150000</v>
@@ -14678,7 +14678,7 @@
         <v>150000</v>
       </c>
       <c r="U102" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15652,10 +15652,10 @@
         <v>570236.66</v>
       </c>
       <c r="S109" t="n">
-        <v>196508.33</v>
+        <v>209898.79</v>
       </c>
       <c r="T109" t="n">
-        <v>197858.33</v>
+        <v>211248.79</v>
       </c>
       <c r="U109" t="n">
         <v>310212.61</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16772,10 +16772,10 @@
         <v>476377.55</v>
       </c>
       <c r="S117" t="n">
-        <v>408381.59</v>
+        <v>418892.49</v>
       </c>
       <c r="T117" t="n">
-        <v>408381.59</v>
+        <v>418892.49</v>
       </c>
       <c r="U117" t="n">
         <v>422635.02</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
         <v>400000</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -19852,10 +19852,10 @@
         <v>100000</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U139" t="n">
         <v>100000</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22652,10 +22652,10 @@
         <v>7880663.77</v>
       </c>
       <c r="S159" t="n">
-        <v>5765246.61</v>
+        <v>6172054.21</v>
       </c>
       <c r="T159" t="n">
-        <v>9350145.01</v>
+        <v>9756952.609999999</v>
       </c>
       <c r="U159" t="n">
         <v>6744400.76</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24180,16 +24180,16 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>1988736.67</v>
+        <v>2039783.04</v>
       </c>
       <c r="P170" t="n">
-        <v>3510552.61</v>
+        <v>3595976.13</v>
       </c>
       <c r="Q170" t="n">
         <v>324976</v>
       </c>
       <c r="R170" t="n">
-        <v>6730981.43</v>
+        <v>6815378.48</v>
       </c>
       <c r="S170" t="n">
         <v>3028966.44</v>
@@ -24198,7 +24198,7 @@
         <v>3172609.32</v>
       </c>
       <c r="U170" t="n">
-        <v>3220428.82</v>
+        <v>3219402.35</v>
       </c>
       <c r="V170" t="n">
         <v>143642.88</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>7919200</v>
+        <v>8756000</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -27555,13 +27555,13 @@
         <v>9640800</v>
       </c>
       <c r="T194" t="n">
-        <v>10594400</v>
+        <v>11926800</v>
       </c>
       <c r="U194" t="n">
         <v>9641600</v>
       </c>
       <c r="V194" t="n">
-        <v>953600</v>
+        <v>2286000</v>
       </c>
       <c r="W194" t="n">
         <v>9665439.67</v>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>146759284.25</v>
+        <v>146839956.6</v>
       </c>
       <c r="P225" t="n">
         <v>51023116.8</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32324,7 +32324,7 @@
         <v>1300000</v>
       </c>
       <c r="W228" t="n">
-        <v>129060346.25</v>
+        <v>120604379.2</v>
       </c>
       <c r="X228" t="n">
         <v>141616875</v>
@@ -32333,10 +32333,10 @@
         <v>4727853</v>
       </c>
       <c r="Z228" t="n">
-        <v>12556528.75</v>
+        <v>21012495.8</v>
       </c>
       <c r="AA228" t="n">
-        <v>129060346.25</v>
+        <v>120604379.2</v>
       </c>
       <c r="AB228" t="n">
         <v>5</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32437,7 +32437,7 @@
         <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>11410039</v>
       </c>
       <c r="O229" t="n">
         <v>64508122.08</v>
@@ -32449,7 +32449,7 @@
         <v>2792377</v>
       </c>
       <c r="R229" t="n">
-        <v>130981425.59</v>
+        <v>142391464.59</v>
       </c>
       <c r="S229" t="n">
         <v>78778260.98999999</v>
@@ -32458,13 +32458,13 @@
         <v>99672054.66</v>
       </c>
       <c r="U229" t="n">
-        <v>79443026</v>
+        <v>90853065</v>
       </c>
       <c r="V229" t="n">
         <v>20893793.67</v>
       </c>
       <c r="W229" t="n">
-        <v>79443026</v>
+        <v>90853065</v>
       </c>
       <c r="X229" t="n">
         <v>83642123</v>
@@ -32476,7 +32476,7 @@
         <v>4199097</v>
       </c>
       <c r="AA229" t="n">
-        <v>79443026</v>
+        <v>90853065</v>
       </c>
       <c r="AB229" t="n">
         <v>5</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>
@@ -33423,7 +33423,7 @@
         <v>39377962.79</v>
       </c>
       <c r="P236" t="n">
-        <v>8829908.050000001</v>
+        <v>8972171.949999999</v>
       </c>
       <c r="Q236" t="n">
         <v>0</v>
@@ -33438,7 +33438,7 @@
         <v>43504495.09</v>
       </c>
       <c r="U236" t="n">
-        <v>44079615.4</v>
+        <v>43937351.5</v>
       </c>
       <c r="V236" t="n">
         <v>1612764.16</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>27/10/2026 12:30:52</t>
+          <t>28/10/2026 13:02:50</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="S5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="T5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="U5" t="n">
-        <v>23976761.62</v>
+        <v>26641116.89</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>48647</v>
       </c>
       <c r="R6" t="n">
-        <v>286378.01</v>
+        <v>332106.01</v>
       </c>
       <c r="S6" t="n">
         <v>138717.61</v>
@@ -1238,7 +1238,7 @@
         <v>187635.95</v>
       </c>
       <c r="U6" t="n">
-        <v>207389.81</v>
+        <v>253117.81</v>
       </c>
       <c r="V6" t="n">
         <v>48918.34</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7637104.25</v>
+        <v>7787045.06</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6095657.28</v>
+        <v>6529580.16</v>
       </c>
       <c r="P10" t="n">
         <v>9822561.83</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -1911,16 +1911,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>231895.55</v>
+        <v>252328.22</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>197487</v>
+        <v>247487</v>
       </c>
       <c r="O11" t="n">
-        <v>209321.41</v>
+        <v>222259.25</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>768736.11</v>
+        <v>818736.11</v>
       </c>
       <c r="S11" t="n">
         <v>568286.11</v>
@@ -1938,13 +1938,13 @@
         <v>731708.33</v>
       </c>
       <c r="U11" t="n">
-        <v>568286.11</v>
+        <v>618286.11</v>
       </c>
       <c r="V11" t="n">
         <v>163422.22</v>
       </c>
       <c r="W11" t="n">
-        <v>569098</v>
+        <v>619098</v>
       </c>
       <c r="X11" t="n">
         <v>371611</v>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>569098</v>
+        <v>619098</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2069,16 +2069,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="S12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="T12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="U12" t="n">
-        <v>4390469.39</v>
+        <v>4897456.04</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2349,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="S14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="T14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="U14" t="n">
-        <v>213403.13</v>
+        <v>235940.81</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4603998.9</v>
+        <v>4615531.98</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1468104.34</v>
+        <v>1468354.97</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1466098.14</v>
+        <v>1466846.74</v>
       </c>
       <c r="P30" t="n">
-        <v>714645.38</v>
+        <v>722244.01</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2815687.13</v>
+        <v>2823285.76</v>
       </c>
       <c r="S30" t="n">
         <v>1923343.7</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>12990006.08</v>
+        <v>13194737.8</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>584278.01</v>
+        <v>640637.0699999999</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>15997.68</v>
+        <v>67878.88</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6409,16 +6409,16 @@
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>356585.57</v>
+        <v>385361.83</v>
       </c>
       <c r="S43" t="n">
-        <v>127313.37</v>
+        <v>128651.49</v>
       </c>
       <c r="T43" t="n">
-        <v>131249.37</v>
+        <v>132587.49</v>
       </c>
       <c r="U43" t="n">
-        <v>180382.12</v>
+        <v>209158.38</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3481169.09</v>
+        <v>3506574.26</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -6951,16 +6951,16 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>202752.63</v>
+        <v>203556.58</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>219000</v>
+        <v>250182</v>
       </c>
       <c r="O47" t="n">
-        <v>182623.58</v>
+        <v>196315.94</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>535000</v>
+        <v>565000</v>
       </c>
       <c r="S47" t="n">
         <v>535000</v>
@@ -6978,13 +6978,13 @@
         <v>535000</v>
       </c>
       <c r="U47" t="n">
-        <v>535000</v>
+        <v>565000</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>535616</v>
+        <v>566798</v>
       </c>
       <c r="X47" t="n">
         <v>316616</v>
@@ -6996,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>535616</v>
+        <v>566798</v>
       </c>
       <c r="AB47" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>46100</v>
       </c>
       <c r="O49" t="n">
-        <v>13906.85</v>
+        <v>20059.96</v>
       </c>
       <c r="P49" t="n">
         <v>8100</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>28785.53</v>
+        <v>30325.94</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
         <v>50000</v>
       </c>
       <c r="O55" t="n">
-        <v>24977.41</v>
+        <v>28656.75</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>417384</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>417384</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>16574.21</v>
+        <v>28974.21</v>
       </c>
       <c r="P107" t="n">
         <v>1830.41</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>130752.4</v>
+        <v>146899.85</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>8492.23</v>
+        <v>11877.7</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>7959.12</v>
+        <v>8298.42</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
         <v>83548.96000000001</v>
       </c>
       <c r="O114" t="n">
-        <v>1690301.29</v>
+        <v>1694326.09</v>
       </c>
       <c r="P114" t="n">
         <v>10732.8</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
         <v>30000</v>
       </c>
       <c r="O117" t="n">
-        <v>212807.32</v>
+        <v>240833.5</v>
       </c>
       <c r="P117" t="n">
         <v>53742.53</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>272291.2</v>
+        <v>304881.63</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>31495.9</v>
+        <v>31642.65</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2078879.83</v>
+        <v>2099337.91</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>184005.97</v>
+        <v>190554.08</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24320,7 +24320,7 @@
         <v>158000</v>
       </c>
       <c r="O171" t="n">
-        <v>174187.05</v>
+        <v>181135.48</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>29737656.95</v>
+        <v>29835796.09</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28404,7 +28404,7 @@
         <v>22000</v>
       </c>
       <c r="W200" t="n">
-        <v>139282</v>
+        <v>58100</v>
       </c>
       <c r="X200" t="n">
         <v>139282</v>
@@ -28413,10 +28413,10 @@
         <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>81182</v>
       </c>
       <c r="AA200" t="n">
-        <v>139282</v>
+        <v>58100</v>
       </c>
       <c r="AB200" t="n">
         <v>5</v>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>148027956.39</v>
+        <v>156788762.85</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31883,25 +31883,25 @@
         <v>146839956.6</v>
       </c>
       <c r="P225" t="n">
-        <v>51023116.8</v>
+        <v>51481812.56</v>
       </c>
       <c r="Q225" t="n">
         <v>5735947</v>
       </c>
       <c r="R225" t="n">
-        <v>224565914.38</v>
+        <v>225004378.08</v>
       </c>
       <c r="S225" t="n">
-        <v>168281233.18</v>
+        <v>168699464.82</v>
       </c>
       <c r="T225" t="n">
-        <v>174619661.81</v>
+        <v>175496589.21</v>
       </c>
       <c r="U225" t="n">
-        <v>173542797.58</v>
+        <v>173522565.52</v>
       </c>
       <c r="V225" t="n">
-        <v>6338428.63</v>
+        <v>6797124.39</v>
       </c>
       <c r="W225" t="n">
         <v>173544257.75</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32291,16 +32291,16 @@
         </is>
       </c>
       <c r="L228" t="n">
+        <v>91071375.70999999</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
         <v>88643125.70999999</v>
-      </c>
-      <c r="M228" t="n">
-        <v>0</v>
-      </c>
-      <c r="N228" t="n">
-        <v>0</v>
-      </c>
-      <c r="O228" t="n">
-        <v>86108915.70999999</v>
       </c>
       <c r="P228" t="n">
         <v>96812362.8</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>68804819.45999999</v>
+        <v>69047985.06</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,7 +32440,7 @@
         <v>11410039</v>
       </c>
       <c r="O229" t="n">
-        <v>64508122.08</v>
+        <v>66282559.74</v>
       </c>
       <c r="P229" t="n">
         <v>51538399.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>39377962.79</v>
+        <v>39615005.05</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -33435,13 +33435,13 @@
         <v>41891730.93</v>
       </c>
       <c r="T236" t="n">
-        <v>43504495.09</v>
+        <v>43535610.23</v>
       </c>
       <c r="U236" t="n">
         <v>43937351.5</v>
       </c>
       <c r="V236" t="n">
-        <v>1612764.16</v>
+        <v>1643879.3</v>
       </c>
       <c r="W236" t="n">
         <v>61292510</v>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>28/10/2026 13:02:50</t>
+          <t>29/10/2026 13:14:49</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6529580.16</v>
+        <v>6530058.96</v>
       </c>
       <c r="P10" t="n">
         <v>9822561.83</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>252328.22</v>
+        <v>267788.5</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>247487</v>
       </c>
       <c r="O11" t="n">
-        <v>222259.25</v>
+        <v>230987.65</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3192,10 +3192,10 @@
         <v>11646331.7</v>
       </c>
       <c r="S20" t="n">
-        <v>5982058.26</v>
+        <v>6462929.77</v>
       </c>
       <c r="T20" t="n">
-        <v>6351244.21</v>
+        <v>6832115.72</v>
       </c>
       <c r="U20" t="n">
         <v>6607543.86</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>11823903.46</v>
+        <v>13080651.9</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1468354.97</v>
+        <v>1469151.34</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1466846.74</v>
+        <v>1467726.86</v>
       </c>
       <c r="P30" t="n">
         <v>722244.01</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4723,13 +4723,13 @@
         <v>3882992.85</v>
       </c>
       <c r="P31" t="n">
-        <v>9202815.26</v>
+        <v>9211307.82</v>
       </c>
       <c r="Q31" t="n">
         <v>36087</v>
       </c>
       <c r="R31" t="n">
-        <v>16406960.26</v>
+        <v>16415452.82</v>
       </c>
       <c r="S31" t="n">
         <v>7080352.51</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>13194737.8</v>
+        <v>13195185.71</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
         <v>12110047.96</v>
       </c>
       <c r="P32" t="n">
-        <v>6186887.32</v>
+        <v>6475693.34</v>
       </c>
       <c r="Q32" t="n">
         <v>103049</v>
       </c>
       <c r="R32" t="n">
-        <v>26432467.54</v>
+        <v>26599467.54</v>
       </c>
       <c r="S32" t="n">
         <v>19923111.37</v>
       </c>
       <c r="T32" t="n">
-        <v>23708075.78</v>
+        <v>23708266.16</v>
       </c>
       <c r="U32" t="n">
-        <v>20245580.22</v>
+        <v>20123774.2</v>
       </c>
       <c r="V32" t="n">
-        <v>3784964.41</v>
+        <v>3785154.79</v>
       </c>
       <c r="W32" t="n">
         <v>20279488</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>559194.2</v>
+        <v>583169.85</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>400000</v>
       </c>
       <c r="O35" t="n">
-        <v>3360002.96</v>
+        <v>3727768.19</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>203556.58</v>
+        <v>207078.66</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>250182</v>
       </c>
       <c r="O47" t="n">
-        <v>196315.94</v>
+        <v>197824.79</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         <v>50000</v>
       </c>
       <c r="O55" t="n">
-        <v>28656.75</v>
+        <v>28785.53</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15503,13 +15503,13 @@
         <v>327691.44</v>
       </c>
       <c r="P108" t="n">
-        <v>150685.93</v>
+        <v>159178.49</v>
       </c>
       <c r="Q108" t="n">
         <v>246945</v>
       </c>
       <c r="R108" t="n">
-        <v>840898.15</v>
+        <v>849390.71</v>
       </c>
       <c r="S108" t="n">
         <v>551969.5</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>8298.42</v>
+        <v>8325.209999999999</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18032,10 +18032,10 @@
         <v>175241.29</v>
       </c>
       <c r="S126" t="n">
-        <v>85742</v>
+        <v>171241.96</v>
       </c>
       <c r="T126" t="n">
-        <v>85742</v>
+        <v>171241.96</v>
       </c>
       <c r="U126" t="n">
         <v>173642</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22652,10 +22652,10 @@
         <v>7880663.77</v>
       </c>
       <c r="S159" t="n">
-        <v>6172054.21</v>
+        <v>6578861.81</v>
       </c>
       <c r="T159" t="n">
-        <v>9756952.609999999</v>
+        <v>10163760.21</v>
       </c>
       <c r="U159" t="n">
         <v>6744400.76</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>31642.65</v>
+        <v>31670.33</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <v>259262</v>
       </c>
       <c r="O168" t="n">
-        <v>151640.37</v>
+        <v>151976.16</v>
       </c>
       <c r="P168" t="n">
         <v>806659.26</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>2039783.04</v>
+        <v>2050640.4</v>
       </c>
       <c r="P170" t="n">
         <v>3595976.13</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>190554.08</v>
+        <v>285527.42</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24320,7 +24320,7 @@
         <v>158000</v>
       </c>
       <c r="O171" t="n">
-        <v>181135.48</v>
+        <v>183930.23</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27692,10 +27692,10 @@
         <v>36906787.78</v>
       </c>
       <c r="S195" t="n">
-        <v>30126000.12</v>
+        <v>30192660.09</v>
       </c>
       <c r="T195" t="n">
-        <v>31060316.58</v>
+        <v>31126976.55</v>
       </c>
       <c r="U195" t="n">
         <v>30921569.47</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28109,7 +28109,7 @@
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>5116854.44</v>
+        <v>5125347</v>
       </c>
       <c r="S198" t="n">
         <v>2474212.01</v>
@@ -28118,7 +28118,7 @@
         <v>2541137.85</v>
       </c>
       <c r="U198" t="n">
-        <v>2502813.93</v>
+        <v>2511306.49</v>
       </c>
       <c r="V198" t="n">
         <v>66925.84</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28252,10 +28252,10 @@
         <v>6089210.8</v>
       </c>
       <c r="S199" t="n">
-        <v>3018930.74</v>
+        <v>3024309.25</v>
       </c>
       <c r="T199" t="n">
-        <v>3123278.5</v>
+        <v>3128657.01</v>
       </c>
       <c r="U199" t="n">
         <v>3323350.49</v>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29792,10 +29792,10 @@
         <v>7852295.06</v>
       </c>
       <c r="S210" t="n">
-        <v>598347.95</v>
+        <v>608259.4399999999</v>
       </c>
       <c r="T210" t="n">
-        <v>2492577.58</v>
+        <v>2502489.07</v>
       </c>
       <c r="U210" t="n">
         <v>2921595.97</v>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>156788762.85</v>
+        <v>160066560.15</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>69047985.06</v>
+        <v>69197789.06</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -32440,7 +32440,7 @@
         <v>11410039</v>
       </c>
       <c r="O229" t="n">
-        <v>66282559.74</v>
+        <v>67182559.73999999</v>
       </c>
       <c r="P229" t="n">
         <v>51538399.59</v>
@@ -32452,10 +32452,10 @@
         <v>142391464.59</v>
       </c>
       <c r="S229" t="n">
-        <v>78778260.98999999</v>
+        <v>78928064.98999999</v>
       </c>
       <c r="T229" t="n">
-        <v>99672054.66</v>
+        <v>99821858.66</v>
       </c>
       <c r="U229" t="n">
         <v>90853065</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>29/10/2026 13:14:49</t>
+          <t>30/10/2026 12:54:02</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202610.xlsx
+++ b/base_despesas/2026/despesas_202610.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>222325.41</v>
+        <v>222827.41</v>
       </c>
       <c r="P7" t="n">
         <v>510399.27</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>1090040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>6530058.96</v>
+        <v>6881077.24</v>
       </c>
       <c r="P10" t="n">
         <v>9822561.83</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>69900.72</v>
+        <v>71840.72</v>
       </c>
       <c r="P17" t="n">
         <v>16525.7</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>600000</v>
       </c>
       <c r="O20" t="n">
-        <v>4054085.21</v>
+        <v>4055251.87</v>
       </c>
       <c r="P20" t="n">
         <v>5038787.84</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1467726.86</v>
+        <v>1467855.72</v>
       </c>
       <c r="P30" t="n">
         <v>722244.01</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>2325144</v>
       </c>
       <c r="O32" t="n">
-        <v>12110047.96</v>
+        <v>12118828.69</v>
       </c>
       <c r="P32" t="n">
         <v>6475693.34</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23200,7 +23200,7 @@
         <v>190000</v>
       </c>
       <c r="O163" t="n">
-        <v>271122.52</v>
+        <v>272222.1</v>
       </c>
       <c r="P163" t="n">
         <v>350343.49</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>211572</v>
       </c>
       <c r="O170" t="n">
-        <v>2050640.4</v>
+        <v>2076638.81</v>
       </c>
       <c r="P170" t="n">
         <v>3595976.13</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27680,7 @@
         <v>8495211.470000001</v>
       </c>
       <c r="O195" t="n">
-        <v>29390686.85</v>
+        <v>29737656.95</v>
       </c>
       <c r="P195" t="n">
         <v>5985218.31</v>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30200,7 +30200,7 @@
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>35300</v>
+        <v>36000</v>
       </c>
       <c r="P213" t="n">
         <v>11400</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>7828675.75</v>
       </c>
       <c r="O225" t="n">
-        <v>146839956.6</v>
+        <v>147590818.24</v>
       </c>
       <c r="P225" t="n">
         <v>51481812.56</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32440,7 @@
         <v>11410039</v>
       </c>
       <c r="O229" t="n">
-        <v>67182559.73999999</v>
+        <v>68172559.73999999</v>
       </c>
       <c r="P229" t="n">
         <v>51538399.59</v>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>30/10/2026 12:54:02</t>
+          <t>31/10/2026 12:27:48</t>
         </is>
       </c>
     </row>
